--- a/data/cards.xlsx
+++ b/data/cards.xlsx
@@ -11,7 +11,7 @@
     <sheet name="填表说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'卡牌数值'!$A$1:$AE$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'卡牌数值'!$A$1:$AK$64</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -105,10 +105,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -485,4670 +485,5588 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE64"/>
+  <dimension ref="A1:AK64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8.055555555555555" customWidth="1" min="1" max="1"/>
-    <col width="10.83333333333333" customWidth="1" min="2" max="2"/>
-    <col width="6.666666666666666" customWidth="1" min="3" max="3"/>
-    <col width="8.611111111111111" customWidth="1" min="4" max="4"/>
-    <col width="34.72222222222222" customWidth="1" min="5" max="5"/>
-    <col width="17.77777777777778" customWidth="1" min="6" max="6"/>
-    <col width="12.22222222222222" customWidth="1" min="7" max="7"/>
-    <col width="19.44444444444444" customWidth="1" min="8" max="8"/>
-    <col width="8.611111111111111" customWidth="1" min="9" max="9"/>
-    <col width="8.611111111111111" customWidth="1" min="10" max="10"/>
-    <col width="8.611111111111111" customWidth="1" min="11" max="11"/>
-    <col width="8.611111111111111" customWidth="1" min="12" max="12"/>
-    <col width="8.611111111111111" customWidth="1" min="13" max="13"/>
-    <col width="8.611111111111111" customWidth="1" min="14" max="14"/>
+    <col width="6.388888888888888" customWidth="1" min="1" max="1"/>
+    <col width="20.83333333333333" customWidth="1" min="2" max="2"/>
+    <col width="10.83333333333333" customWidth="1" min="3" max="3"/>
+    <col width="15.27777777777778" customWidth="1" min="4" max="4"/>
+    <col width="6.666666666666666" customWidth="1" min="5" max="5"/>
+    <col width="8.611111111111111" customWidth="1" min="6" max="6"/>
+    <col width="34.72222222222222" customWidth="1" min="7" max="7"/>
+    <col width="17.77777777777778" customWidth="1" min="8" max="8"/>
+    <col width="12.22222222222222" customWidth="1" min="9" max="9"/>
+    <col width="8.888888888888889" customWidth="1" min="10" max="10"/>
+    <col width="7.222222222222222" customWidth="1" min="11" max="11"/>
+    <col width="8.333333333333334" customWidth="1" min="12" max="12"/>
+    <col width="6.666666666666666" customWidth="1" min="13" max="13"/>
+    <col width="19.44444444444444" customWidth="1" min="14" max="14"/>
     <col width="8.611111111111111" customWidth="1" min="15" max="15"/>
     <col width="8.611111111111111" customWidth="1" min="16" max="16"/>
     <col width="8.611111111111111" customWidth="1" min="17" max="17"/>
-    <col width="11.38888888888889" customWidth="1" min="18" max="18"/>
-    <col width="10.83333333333333" customWidth="1" min="19" max="19"/>
-    <col width="19.44444444444444" customWidth="1" min="20" max="20"/>
+    <col width="8.611111111111111" customWidth="1" min="18" max="18"/>
+    <col width="8.611111111111111" customWidth="1" min="19" max="19"/>
+    <col width="8.611111111111111" customWidth="1" min="20" max="20"/>
     <col width="8.611111111111111" customWidth="1" min="21" max="21"/>
     <col width="8.611111111111111" customWidth="1" min="22" max="22"/>
     <col width="8.611111111111111" customWidth="1" min="23" max="23"/>
-    <col width="8.611111111111111" customWidth="1" min="24" max="24"/>
-    <col width="8.611111111111111" customWidth="1" min="25" max="25"/>
-    <col width="8.611111111111111" customWidth="1" min="26" max="26"/>
+    <col width="11.38888888888889" customWidth="1" min="24" max="24"/>
+    <col width="10.83333333333333" customWidth="1" min="25" max="25"/>
+    <col width="19.44444444444444" customWidth="1" min="26" max="26"/>
     <col width="8.611111111111111" customWidth="1" min="27" max="27"/>
     <col width="8.611111111111111" customWidth="1" min="28" max="28"/>
     <col width="8.611111111111111" customWidth="1" min="29" max="29"/>
-    <col width="11.38888888888889" customWidth="1" min="30" max="30"/>
-    <col width="10.83333333333333" customWidth="1" min="31" max="31"/>
+    <col width="8.611111111111111" customWidth="1" min="30" max="30"/>
+    <col width="8.611111111111111" customWidth="1" min="31" max="31"/>
+    <col width="8.611111111111111" customWidth="1" min="32" max="32"/>
+    <col width="8.611111111111111" customWidth="1" min="33" max="33"/>
+    <col width="8.611111111111111" customWidth="1" min="34" max="34"/>
+    <col width="8.611111111111111" customWidth="1" min="35" max="35"/>
+    <col width="11.38888888888889" customWidth="1" min="36" max="36"/>
+    <col width="10.83333333333333" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>谁</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>whoId</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>头像</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>分类</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>卡面文案</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>出现条件</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>自带状态</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>窗口</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>单局一次</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>隐藏</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>左·文案</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>左·spend</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>左·buy</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>左·sell</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>左·borrow</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>左·repay</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>左·cash</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>左·mind</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>左·risk</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>左·social</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>左·加状态</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>左·清状态</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>右·文案</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>右·spend</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>右·buy</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>右·sell</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>右·borrow</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>右·repay</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>右·cash</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>右·mind</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>右·risk</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>右·social</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>右·加状态</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>右·清状态</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>c001</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="3" t="inlineStr">
         <is>
+          <t>fam_mortgage_01</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>老婆</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>laopo</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>💍</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>家庭</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>这个月房贷 6,800。你看着办。</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr"/>
-      <c r="G2" s="3" t="inlineStr"/>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>先拖两天</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr"/>
-      <c r="J2" s="3" t="inlineStr"/>
-      <c r="K2" s="3" t="inlineStr"/>
-      <c r="L2" s="3" t="inlineStr"/>
-      <c r="M2" s="3" t="inlineStr"/>
-      <c r="N2" s="3" t="inlineStr"/>
-      <c r="O2" s="4" t="n">
+      <c r="O2" s="2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr"/>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr"/>
+      <c r="U2" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="P2" s="3" t="inlineStr"/>
-      <c r="Q2" s="4" t="n">
+      <c r="V2" s="2" t="inlineStr"/>
+      <c r="W2" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr"/>
-      <c r="T2" s="3" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>出 5,500</t>
         </is>
       </c>
-      <c r="U2" s="5" t="n">
+      <c r="AA2" s="5" t="n">
         <v>5500</v>
       </c>
-      <c r="V2" s="3" t="inlineStr"/>
-      <c r="W2" s="3" t="inlineStr"/>
-      <c r="X2" s="3" t="inlineStr"/>
-      <c r="Y2" s="3" t="inlineStr"/>
-      <c r="Z2" s="3" t="inlineStr"/>
-      <c r="AA2" s="5" t="n">
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+      <c r="AG2" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="AB2" s="3" t="inlineStr"/>
-      <c r="AC2" s="5" t="n">
+      <c r="AH2" s="2" t="inlineStr"/>
+      <c r="AI2" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="AD2" s="3" t="inlineStr"/>
-      <c r="AE2" s="3" t="inlineStr"/>
+      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AK2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>c002</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="3" t="inlineStr">
         <is>
+          <t>fam_tutor_01</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>老婆</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>laopo</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>💍</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>家庭</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>孩子要上补习班，一年两万八。</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr"/>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>太贵了，不报</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr"/>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="4" t="n">
+      <c r="O3" s="2" t="inlineStr"/>
+      <c r="P3" s="2" t="inlineStr"/>
+      <c r="Q3" s="2" t="inlineStr"/>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr"/>
+      <c r="U3" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="P3" s="3" t="inlineStr"/>
-      <c r="Q3" s="4" t="n">
+      <c r="V3" s="2" t="inlineStr"/>
+      <c r="W3" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>出 3,900 报名</t>
         </is>
       </c>
-      <c r="U3" s="5" t="n">
+      <c r="AA3" s="5" t="n">
         <v>3900</v>
       </c>
-      <c r="V3" s="3" t="inlineStr"/>
-      <c r="W3" s="3" t="inlineStr"/>
-      <c r="X3" s="3" t="inlineStr"/>
-      <c r="Y3" s="3" t="inlineStr"/>
-      <c r="Z3" s="3" t="inlineStr"/>
-      <c r="AA3" s="5" t="n">
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr"/>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AG3" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="AB3" s="3" t="inlineStr"/>
-      <c r="AC3" s="5" t="n">
+      <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="AD3" s="3" t="inlineStr"/>
-      <c r="AE3" s="3" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
+      <c r="AK3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>c003</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>fam_confess_01</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>老婆</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>laopo</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>💍</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>家庭</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>你到底亏了多少？我要听实话。</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr"/>
-      <c r="G4" s="3" t="inlineStr"/>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>报喜不报忧</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr"/>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
-      <c r="L4" s="3" t="inlineStr"/>
-      <c r="M4" s="3" t="inlineStr"/>
-      <c r="N4" s="3" t="inlineStr"/>
-      <c r="O4" s="4" t="n">
+      <c r="O4" s="2" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="P4" s="3" t="inlineStr"/>
-      <c r="Q4" s="4" t="n">
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
-      <c r="T4" s="3" t="inlineStr">
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>说实话</t>
         </is>
       </c>
-      <c r="U4" s="3" t="inlineStr"/>
-      <c r="V4" s="3" t="inlineStr"/>
-      <c r="W4" s="3" t="inlineStr"/>
-      <c r="X4" s="3" t="inlineStr"/>
-      <c r="Y4" s="3" t="inlineStr"/>
-      <c r="Z4" s="3" t="inlineStr"/>
-      <c r="AA4" s="4" t="n">
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AG4" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="AB4" s="3" t="inlineStr"/>
-      <c r="AC4" s="5" t="n">
+      <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AI4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="AD4" s="3" t="inlineStr"/>
-      <c r="AE4" s="3" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr"/>
+      <c r="AK4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>c004</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>fam_dinner_01</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>老婆</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>laopo</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>💍</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>家庭</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>我们多久没一起吃饭了？</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>最近有点忙</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr"/>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="3" t="inlineStr"/>
-      <c r="L5" s="3" t="inlineStr"/>
-      <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="4" t="n">
+      <c r="O5" s="2" t="inlineStr"/>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="P5" s="3" t="inlineStr"/>
-      <c r="Q5" s="4" t="n">
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="4" t="n">
         <v>-7</v>
       </c>
-      <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="X5" s="2" t="inlineStr"/>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>出去吃，我请</t>
         </is>
       </c>
-      <c r="U5" s="5" t="n">
+      <c r="AA5" s="5" t="n">
         <v>1200</v>
       </c>
-      <c r="V5" s="3" t="inlineStr"/>
-      <c r="W5" s="3" t="inlineStr"/>
-      <c r="X5" s="3" t="inlineStr"/>
-      <c r="Y5" s="3" t="inlineStr"/>
-      <c r="Z5" s="3" t="inlineStr"/>
-      <c r="AA5" s="5" t="n">
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="AB5" s="3" t="inlineStr"/>
-      <c r="AC5" s="5" t="n">
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="AD5" s="3" t="inlineStr"/>
-      <c r="AE5" s="3" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+      <c r="AK5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>c005</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
+          <t>fam_pregnant_01</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>老婆</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>laopo</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>💍</t>
         </is>
       </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>家庭</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>我怀孕了。</t>
         </is>
       </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>no:baby</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>现在不合适</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr"/>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
-      <c r="L6" s="3" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="3" t="inlineStr"/>
-      <c r="O6" s="4" t="n">
+      <c r="O6" s="2" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="4" t="n">
         <v>-12</v>
       </c>
-      <c r="P6" s="3" t="inlineStr"/>
-      <c r="Q6" s="4" t="n">
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="4" t="n">
         <v>-14</v>
       </c>
-      <c r="R6" s="3" t="inlineStr"/>
-      <c r="S6" s="3" t="inlineStr"/>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>留着吧</t>
         </is>
       </c>
-      <c r="U6" s="5" t="n">
+      <c r="AA6" s="5" t="n">
         <v>5200</v>
       </c>
-      <c r="V6" s="3" t="inlineStr"/>
-      <c r="W6" s="3" t="inlineStr"/>
-      <c r="X6" s="3" t="inlineStr"/>
-      <c r="Y6" s="3" t="inlineStr"/>
-      <c r="Z6" s="3" t="inlineStr"/>
-      <c r="AA6" s="5" t="n">
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="AB6" s="3" t="inlineStr"/>
-      <c r="AC6" s="5" t="n">
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="AD6" s="3" t="inlineStr">
+      <c r="AJ6" s="2" t="inlineStr">
         <is>
           <t>baby:-1</t>
         </is>
       </c>
-      <c r="AE6" s="3" t="inlineStr"/>
+      <c r="AK6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>c006</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
+          <t>fam_divorce_01</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
           <t>老婆</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>laopo</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>💍</t>
         </is>
       </c>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>家庭</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>这日子没法过了。离婚吧。</t>
         </is>
       </c>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>mind&lt;30</t>
         </is>
       </c>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>……好</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr"/>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="3" t="inlineStr"/>
-      <c r="L7" s="3" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
-      <c r="N7" s="4" t="n">
+      <c r="O7" s="2" t="inlineStr"/>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="4" t="n">
         <v>-3000</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="U7" s="4" t="n">
         <v>-14</v>
       </c>
-      <c r="P7" s="3" t="inlineStr"/>
-      <c r="Q7" s="4" t="n">
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="4" t="n">
         <v>-20</v>
       </c>
-      <c r="R7" s="3" t="inlineStr"/>
-      <c r="S7" s="3" t="inlineStr"/>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr">
         <is>
           <t>挽留，转 5,800</t>
         </is>
       </c>
-      <c r="U7" s="5" t="n">
+      <c r="AA7" s="5" t="n">
         <v>5800</v>
       </c>
-      <c r="V7" s="3" t="inlineStr"/>
-      <c r="W7" s="3" t="inlineStr"/>
-      <c r="X7" s="3" t="inlineStr"/>
-      <c r="Y7" s="3" t="inlineStr"/>
-      <c r="Z7" s="3" t="inlineStr"/>
-      <c r="AA7" s="5" t="n">
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="AB7" s="3" t="inlineStr"/>
-      <c r="AC7" s="5" t="n">
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="AD7" s="3" t="inlineStr"/>
-      <c r="AE7" s="3" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+      <c r="AK7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>c007</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>fam_daughter_01</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
           <t>女儿</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>nver</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>👧</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>家庭</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>爸爸，你为什么总在看手机？</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr"/>
-      <c r="G8" s="3" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>陪她玩一会儿</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr"/>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
-      <c r="L8" s="3" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr"/>
-      <c r="N8" s="3" t="inlineStr"/>
-      <c r="O8" s="5" t="n">
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="P8" s="3" t="inlineStr"/>
-      <c r="Q8" s="5" t="n">
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr"/>
-      <c r="T8" s="3" t="inlineStr">
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr">
         <is>
           <t>爸爸在工作</t>
         </is>
       </c>
-      <c r="U8" s="3" t="inlineStr"/>
-      <c r="V8" s="3" t="inlineStr"/>
-      <c r="W8" s="3" t="inlineStr"/>
-      <c r="X8" s="3" t="inlineStr"/>
-      <c r="Y8" s="3" t="inlineStr"/>
-      <c r="Z8" s="3" t="inlineStr"/>
-      <c r="AA8" s="4" t="n">
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="AB8" s="3" t="inlineStr"/>
-      <c r="AC8" s="4" t="n">
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="AD8" s="3" t="inlineStr"/>
-      <c r="AE8" s="3" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+      <c r="AK8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>c008</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
+          <t>fam_parentmeet_01</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
           <t>老师</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>laoshi</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>🏫</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>家庭</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>今晚家长会，你来不来？</t>
         </is>
       </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>让妈妈去吧</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr"/>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="3" t="inlineStr"/>
-      <c r="L9" s="3" t="inlineStr"/>
-      <c r="M9" s="3" t="inlineStr"/>
-      <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="4" t="n">
+      <c r="O9" s="2" t="inlineStr"/>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="4" t="n">
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="4" t="n">
         <v>-7</v>
       </c>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr"/>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="X9" s="2" t="inlineStr"/>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr">
         <is>
           <t>我去</t>
         </is>
       </c>
-      <c r="U9" s="3" t="inlineStr"/>
-      <c r="V9" s="3" t="inlineStr"/>
-      <c r="W9" s="3" t="inlineStr"/>
-      <c r="X9" s="3" t="inlineStr"/>
-      <c r="Y9" s="3" t="inlineStr"/>
-      <c r="Z9" s="3" t="inlineStr"/>
-      <c r="AA9" s="5" t="n">
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="AB9" s="3" t="inlineStr"/>
-      <c r="AC9" s="5" t="n">
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="AD9" s="3" t="inlineStr"/>
-      <c r="AE9" s="3" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+      <c r="AK9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>c009</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
+          <t>fam_hospital_01</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
           <t>老妈</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>laoma</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>👵</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>家庭</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>你爸住院了，要先垫三万。</t>
         </is>
       </c>
-      <c r="F10" s="3" t="inlineStr"/>
-      <c r="G10" s="3" t="inlineStr"/>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>让弟弟先垫</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr"/>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="3" t="inlineStr"/>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr"/>
-      <c r="N10" s="3" t="inlineStr"/>
-      <c r="O10" s="4" t="n">
+      <c r="O10" s="2" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="4" t="n">
         <v>-7</v>
       </c>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="4" t="n">
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="4" t="n">
         <v>-11</v>
       </c>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr"/>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="X10" s="2" t="inlineStr"/>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>我出 6,500</t>
         </is>
       </c>
-      <c r="U10" s="5" t="n">
+      <c r="AA10" s="5" t="n">
         <v>6500</v>
       </c>
-      <c r="V10" s="3" t="inlineStr"/>
-      <c r="W10" s="3" t="inlineStr"/>
-      <c r="X10" s="3" t="inlineStr"/>
-      <c r="Y10" s="3" t="inlineStr"/>
-      <c r="Z10" s="3" t="inlineStr"/>
-      <c r="AA10" s="5" t="n">
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="AB10" s="3" t="inlineStr"/>
-      <c r="AC10" s="5" t="n">
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="AD10" s="3" t="inlineStr"/>
-      <c r="AE10" s="3" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+      <c r="AK10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>c010</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
+          <t>fam_eldermoney_01</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
           <t>老妈</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>laoma</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>👵</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>家庭</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>我这有二十万养老钱，你拿去做，赚了都是你的。</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr"/>
-      <c r="G11" s="3" t="inlineStr"/>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>妈，这个不能要</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="3" t="inlineStr"/>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr"/>
-      <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="5" t="n">
+      <c r="O11" s="2" t="inlineStr"/>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="5" t="n">
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="X11" s="2" t="inlineStr"/>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr">
         <is>
           <t>收下，投进去</t>
         </is>
       </c>
-      <c r="U11" s="3" t="inlineStr"/>
-      <c r="V11" s="3" t="inlineStr"/>
-      <c r="W11" s="3" t="inlineStr"/>
-      <c r="X11" s="5" t="n">
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="5" t="n">
         <v>12000</v>
       </c>
-      <c r="Y11" s="3" t="inlineStr"/>
-      <c r="Z11" s="3" t="inlineStr"/>
-      <c r="AA11" s="4" t="n">
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="4" t="n">
         <v>-9</v>
       </c>
-      <c r="AB11" s="3" t="inlineStr"/>
-      <c r="AC11" s="4" t="n">
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="AD11" s="3" t="inlineStr"/>
-      <c r="AE11" s="3" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+      <c r="AK11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>c011</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>fam_inlaws_01</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
           <t>丈母娘</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>zhangmuniang</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>🧓</t>
         </is>
       </c>
-      <c r="D12" s="3" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>家庭</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>听说你最近在做投资？妈这里有点闲钱。</t>
         </is>
       </c>
-      <c r="F12" s="3" t="inlineStr"/>
-      <c r="G12" s="3" t="inlineStr"/>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>您留着养老</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr"/>
-      <c r="J12" s="3" t="inlineStr"/>
-      <c r="K12" s="3" t="inlineStr"/>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr"/>
-      <c r="N12" s="3" t="inlineStr"/>
-      <c r="O12" s="5" t="n">
+      <c r="O12" s="2" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="5" t="n">
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr">
+      <c r="X12" s="2" t="inlineStr"/>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr">
         <is>
           <t>拿 20,000</t>
         </is>
       </c>
-      <c r="U12" s="3" t="inlineStr"/>
-      <c r="V12" s="3" t="inlineStr"/>
-      <c r="W12" s="3" t="inlineStr"/>
-      <c r="X12" s="5" t="n">
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="5" t="n">
         <v>15000</v>
       </c>
-      <c r="Y12" s="3" t="inlineStr"/>
-      <c r="Z12" s="3" t="inlineStr"/>
-      <c r="AA12" s="4" t="n">
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="4" t="n">
         <v>-8</v>
       </c>
-      <c r="AB12" s="3" t="inlineStr"/>
-      <c r="AC12" s="4" t="n">
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AD12" s="3" t="inlineStr"/>
-      <c r="AE12" s="3" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+      <c r="AK12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>c012</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
+          <t>fam_fever_01</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>孩子</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>haizi</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>🤒</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>家庭</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>半夜发烧 39 度。</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>has:baby</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>先观察一晚</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr"/>
-      <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="3" t="inlineStr"/>
-      <c r="L13" s="3" t="inlineStr"/>
-      <c r="M13" s="3" t="inlineStr"/>
-      <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="4" t="n">
+      <c r="O13" s="2" t="inlineStr"/>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="4" t="n">
         <v>-7</v>
       </c>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="4" t="n">
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="4" t="n">
         <v>-8</v>
       </c>
-      <c r="R13" s="3" t="inlineStr"/>
-      <c r="S13" s="3" t="inlineStr"/>
-      <c r="T13" s="3" t="inlineStr">
+      <c r="X13" s="2" t="inlineStr"/>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr">
         <is>
           <t>连夜去医院</t>
         </is>
       </c>
-      <c r="U13" s="5" t="n">
+      <c r="AA13" s="5" t="n">
         <v>1600</v>
       </c>
-      <c r="V13" s="3" t="inlineStr"/>
-      <c r="W13" s="3" t="inlineStr"/>
-      <c r="X13" s="3" t="inlineStr"/>
-      <c r="Y13" s="3" t="inlineStr"/>
-      <c r="Z13" s="3" t="inlineStr"/>
-      <c r="AA13" s="4" t="n">
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="AB13" s="3" t="inlineStr"/>
-      <c r="AC13" s="5" t="n">
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="AD13" s="3" t="inlineStr"/>
-      <c r="AE13" s="3" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+      <c r="AK13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>c013</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
+          <t>fam_babysfirst_01</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>孩子</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>haizi</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>👶</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>家庭</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>他第一次叫爸爸。你正在看盘。</t>
         </is>
       </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>has:baby</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>把他抱起来</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr"/>
-      <c r="J14" s="3" t="inlineStr"/>
-      <c r="K14" s="3" t="inlineStr"/>
-      <c r="L14" s="3" t="inlineStr"/>
-      <c r="M14" s="3" t="inlineStr"/>
-      <c r="N14" s="3" t="inlineStr"/>
-      <c r="O14" s="5" t="n">
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="5" t="n">
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr"/>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="X14" s="2" t="inlineStr"/>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr">
         <is>
           <t>再看一会儿</t>
         </is>
       </c>
-      <c r="U14" s="3" t="inlineStr"/>
-      <c r="V14" s="3" t="inlineStr"/>
-      <c r="W14" s="3" t="inlineStr"/>
-      <c r="X14" s="3" t="inlineStr"/>
-      <c r="Y14" s="3" t="inlineStr"/>
-      <c r="Z14" s="3" t="inlineStr"/>
-      <c r="AA14" s="4" t="n">
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="AB14" s="3" t="inlineStr"/>
-      <c r="AC14" s="4" t="n">
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AD14" s="3" t="inlineStr"/>
-      <c r="AE14" s="3" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+      <c r="AK14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>c014</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
+          <t>fam_rent_01</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
           <t>房东</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>fangdong</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>🏠</t>
         </is>
       </c>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>家庭</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>下个月房租要涨 800。</t>
         </is>
       </c>
-      <c r="F15" s="3" t="inlineStr"/>
-      <c r="G15" s="3" t="inlineStr"/>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>搬家</t>
         </is>
       </c>
-      <c r="I15" s="5" t="n">
+      <c r="O15" s="5" t="n">
         <v>2100</v>
       </c>
-      <c r="J15" s="3" t="inlineStr"/>
-      <c r="K15" s="3" t="inlineStr"/>
-      <c r="L15" s="3" t="inlineStr"/>
-      <c r="M15" s="3" t="inlineStr"/>
-      <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="4" t="n">
+      <c r="P15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="P15" s="3" t="inlineStr"/>
-      <c r="Q15" s="4" t="n">
+      <c r="V15" s="2" t="inlineStr"/>
+      <c r="W15" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="R15" s="3" t="inlineStr"/>
-      <c r="S15" s="3" t="inlineStr"/>
-      <c r="T15" s="3" t="inlineStr">
+      <c r="X15" s="2" t="inlineStr"/>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr">
         <is>
           <t>认了</t>
         </is>
       </c>
-      <c r="U15" s="5" t="n">
+      <c r="AA15" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="V15" s="3" t="inlineStr"/>
-      <c r="W15" s="3" t="inlineStr"/>
-      <c r="X15" s="3" t="inlineStr"/>
-      <c r="Y15" s="3" t="inlineStr"/>
-      <c r="Z15" s="3" t="inlineStr"/>
-      <c r="AA15" s="3" t="inlineStr"/>
-      <c r="AB15" s="3" t="inlineStr"/>
-      <c r="AC15" s="5" t="n">
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr"/>
+      <c r="AI15" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="AD15" s="3" t="inlineStr"/>
-      <c r="AE15" s="3" t="inlineStr"/>
+      <c r="AJ15" s="2" t="inlineStr"/>
+      <c r="AK15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>c015</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
+          <t>work_layoff_01</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
           <t>老板</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>laoban</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>😰</t>
         </is>
       </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>职场</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>公司要优化，名单下周公布，你心里有个数。</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr"/>
-      <c r="G16" s="3" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>多陪陪家人</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr"/>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="3" t="inlineStr"/>
-      <c r="L16" s="3" t="inlineStr"/>
-      <c r="M16" s="3" t="inlineStr"/>
-      <c r="N16" s="3" t="inlineStr"/>
-      <c r="O16" s="4" t="n">
+      <c r="O16" s="2" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr"/>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="P16" s="3" t="inlineStr"/>
-      <c r="Q16" s="5" t="n">
+      <c r="V16" s="2" t="inlineStr"/>
+      <c r="W16" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="R16" s="3" t="inlineStr"/>
-      <c r="S16" s="3" t="inlineStr"/>
-      <c r="T16" s="3" t="inlineStr">
+      <c r="X16" s="2" t="inlineStr"/>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr">
         <is>
           <t>赌一把，加仓</t>
         </is>
       </c>
-      <c r="U16" s="3" t="inlineStr"/>
-      <c r="V16" s="5" t="n">
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="5" t="n">
         <v>4000</v>
       </c>
-      <c r="W16" s="3" t="inlineStr"/>
-      <c r="X16" s="3" t="inlineStr"/>
-      <c r="Y16" s="3" t="inlineStr"/>
-      <c r="Z16" s="3" t="inlineStr"/>
-      <c r="AA16" s="4" t="n">
+      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="AB16" s="3" t="inlineStr"/>
-      <c r="AC16" s="3" t="inlineStr"/>
-      <c r="AD16" s="3" t="inlineStr"/>
-      <c r="AE16" s="3" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr"/>
+      <c r="AI16" s="2" t="inlineStr"/>
+      <c r="AJ16" s="2" t="inlineStr"/>
+      <c r="AK16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>c016</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
+          <t>work_options_01</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
           <t>老板</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>laoban</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>😰</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>职场</t>
         </is>
       </c>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>今年年终奖取消，改成期权，大家理解一下。</t>
         </is>
       </c>
-      <c r="F17" s="3" t="inlineStr"/>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>我不理解</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr"/>
-      <c r="J17" s="3" t="inlineStr"/>
-      <c r="K17" s="3" t="inlineStr"/>
-      <c r="L17" s="3" t="inlineStr"/>
-      <c r="M17" s="3" t="inlineStr"/>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="4" t="n">
+      <c r="O17" s="2" t="inlineStr"/>
+      <c r="P17" s="2" t="inlineStr"/>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="P17" s="3" t="inlineStr"/>
-      <c r="Q17" s="4" t="n">
+      <c r="V17" s="2" t="inlineStr"/>
+      <c r="W17" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="R17" s="3" t="inlineStr"/>
-      <c r="S17" s="3" t="inlineStr"/>
-      <c r="T17" s="3" t="inlineStr">
+      <c r="X17" s="2" t="inlineStr"/>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr">
         <is>
           <t>理解</t>
         </is>
       </c>
-      <c r="U17" s="3" t="inlineStr"/>
-      <c r="V17" s="3" t="inlineStr"/>
-      <c r="W17" s="3" t="inlineStr"/>
-      <c r="X17" s="3" t="inlineStr"/>
-      <c r="Y17" s="3" t="inlineStr"/>
-      <c r="Z17" s="3" t="inlineStr"/>
-      <c r="AA17" s="4" t="n">
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr"/>
+      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="AB17" s="3" t="inlineStr"/>
-      <c r="AC17" s="5" t="n">
+      <c r="AH17" s="2" t="inlineStr"/>
+      <c r="AI17" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="AD17" s="3" t="inlineStr"/>
-      <c r="AE17" s="3" t="inlineStr"/>
+      <c r="AJ17" s="2" t="inlineStr"/>
+      <c r="AK17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>c017</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
+          <t>work_fired_01</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
           <t>HR</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>📦</t>
         </is>
       </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>职场</t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>HR 找你聊了十分钟。工位上的东西，你可以明天来收拾。</t>
         </is>
       </c>
-      <c r="F18" s="3" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>no:fired</t>
         </is>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>fired:-1</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>我早就不想干了</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="3" t="inlineStr"/>
-      <c r="L18" s="3" t="inlineStr"/>
-      <c r="M18" s="3" t="inlineStr"/>
-      <c r="N18" s="5" t="n">
+      <c r="O18" s="2" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr"/>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="5" t="n">
         <v>8000</v>
       </c>
-      <c r="O18" s="4" t="n">
+      <c r="U18" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="P18" s="3" t="inlineStr"/>
-      <c r="Q18" s="4" t="n">
+      <c r="V18" s="2" t="inlineStr"/>
+      <c r="W18" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="R18" s="3" t="inlineStr"/>
-      <c r="S18" s="3" t="inlineStr"/>
-      <c r="T18" s="3" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr"/>
+      <c r="Y18" s="2" t="inlineStr"/>
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>再给我一次机会</t>
         </is>
       </c>
-      <c r="U18" s="3" t="inlineStr"/>
-      <c r="V18" s="3" t="inlineStr"/>
-      <c r="W18" s="3" t="inlineStr"/>
-      <c r="X18" s="3" t="inlineStr"/>
-      <c r="Y18" s="3" t="inlineStr"/>
-      <c r="Z18" s="3" t="inlineStr"/>
-      <c r="AA18" s="4" t="n">
+      <c r="AA18" s="2" t="inlineStr"/>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AD18" s="2" t="inlineStr"/>
+      <c r="AE18" s="2" t="inlineStr"/>
+      <c r="AF18" s="2" t="inlineStr"/>
+      <c r="AG18" s="4" t="n">
         <v>-9</v>
       </c>
-      <c r="AB18" s="3" t="inlineStr"/>
-      <c r="AC18" s="4" t="n">
+      <c r="AH18" s="2" t="inlineStr"/>
+      <c r="AI18" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AD18" s="3" t="inlineStr"/>
-      <c r="AE18" s="3" t="inlineStr"/>
+      <c r="AJ18" s="2" t="inlineStr"/>
+      <c r="AK18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>c018</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
+          <t>work_jobhunt_01</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
           <t>招聘软件</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>zhaopin</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>📱</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>职场</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>对方已读，没有回。</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>has:fired</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr"/>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>先接点零活</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="3" t="inlineStr"/>
-      <c r="L19" s="3" t="inlineStr"/>
-      <c r="M19" s="3" t="inlineStr"/>
-      <c r="N19" s="5" t="n">
+      <c r="O19" s="2" t="inlineStr"/>
+      <c r="P19" s="2" t="inlineStr"/>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="5" t="n">
         <v>2500</v>
       </c>
-      <c r="O19" s="4" t="n">
+      <c r="U19" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="P19" s="3" t="inlineStr"/>
-      <c r="Q19" s="5" t="n">
+      <c r="V19" s="2" t="inlineStr"/>
+      <c r="W19" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="R19" s="3" t="inlineStr"/>
-      <c r="S19" s="3" t="inlineStr"/>
-      <c r="T19" s="3" t="inlineStr">
+      <c r="X19" s="2" t="inlineStr"/>
+      <c r="Y19" s="2" t="inlineStr"/>
+      <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>再降低点期望</t>
         </is>
       </c>
-      <c r="U19" s="3" t="inlineStr"/>
-      <c r="V19" s="3" t="inlineStr"/>
-      <c r="W19" s="3" t="inlineStr"/>
-      <c r="X19" s="3" t="inlineStr"/>
-      <c r="Y19" s="3" t="inlineStr"/>
-      <c r="Z19" s="3" t="inlineStr"/>
-      <c r="AA19" s="4" t="n">
+      <c r="AA19" s="2" t="inlineStr"/>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AD19" s="2" t="inlineStr"/>
+      <c r="AE19" s="2" t="inlineStr"/>
+      <c r="AF19" s="2" t="inlineStr"/>
+      <c r="AG19" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="AB19" s="3" t="inlineStr"/>
-      <c r="AC19" s="4" t="n">
+      <c r="AH19" s="2" t="inlineStr"/>
+      <c r="AI19" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="AD19" s="3" t="inlineStr"/>
-      <c r="AE19" s="3" t="inlineStr"/>
+      <c r="AJ19" s="2" t="inlineStr"/>
+      <c r="AK19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>c019</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
+          <t>work_offer_01</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
           <t>老同事</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>laotongshi</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>🤝</t>
         </is>
       </c>
-      <c r="D20" s="3" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>职场</t>
         </is>
       </c>
-      <c r="E20" s="3" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>我们组缺人，就是降薪三成。来不来？</t>
         </is>
       </c>
-      <c r="F20" s="3" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>has:fired; social&gt;52</t>
         </is>
       </c>
-      <c r="G20" s="3" t="inlineStr"/>
-      <c r="H20" s="3" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr"/>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>再等等</t>
         </is>
       </c>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
-      <c r="L20" s="3" t="inlineStr"/>
-      <c r="M20" s="3" t="inlineStr"/>
-      <c r="N20" s="3" t="inlineStr"/>
-      <c r="O20" s="4" t="n">
+      <c r="O20" s="2" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr"/>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="P20" s="3" t="inlineStr"/>
-      <c r="Q20" s="3" t="inlineStr"/>
-      <c r="R20" s="3" t="inlineStr"/>
-      <c r="S20" s="3" t="inlineStr"/>
-      <c r="T20" s="3" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr"/>
+      <c r="W20" s="2" t="inlineStr"/>
+      <c r="X20" s="2" t="inlineStr"/>
+      <c r="Y20" s="2" t="inlineStr"/>
+      <c r="Z20" s="2" t="inlineStr">
         <is>
           <t>来</t>
         </is>
       </c>
-      <c r="U20" s="3" t="inlineStr"/>
-      <c r="V20" s="3" t="inlineStr"/>
-      <c r="W20" s="3" t="inlineStr"/>
-      <c r="X20" s="3" t="inlineStr"/>
-      <c r="Y20" s="3" t="inlineStr"/>
-      <c r="Z20" s="5" t="n">
+      <c r="AA20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr"/>
+      <c r="AD20" s="2" t="inlineStr"/>
+      <c r="AE20" s="2" t="inlineStr"/>
+      <c r="AF20" s="5" t="n">
         <v>3000</v>
       </c>
-      <c r="AA20" s="5" t="n">
+      <c r="AG20" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="AB20" s="3" t="inlineStr"/>
-      <c r="AC20" s="5" t="n">
+      <c r="AH20" s="2" t="inlineStr"/>
+      <c r="AI20" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="AD20" s="3" t="inlineStr"/>
-      <c r="AE20" s="3" t="inlineStr">
+      <c r="AJ20" s="2" t="inlineStr"/>
+      <c r="AK20" s="2" t="inlineStr">
         <is>
           <t>fired</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>c020</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
+          <t>work_gossip_01</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
           <t>同事</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>tongshi</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>☕</t>
         </is>
       </c>
-      <c r="D21" s="3" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>职场</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>茶水间都在聊这只票，已经连着涨好几天了。</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr"/>
-      <c r="G21" s="3" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>不接最后一棒</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr"/>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="3" t="inlineStr"/>
-      <c r="L21" s="3" t="inlineStr"/>
-      <c r="M21" s="3" t="inlineStr"/>
-      <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="5" t="n">
+      <c r="O21" s="2" t="inlineStr"/>
+      <c r="P21" s="2" t="inlineStr"/>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="P21" s="3" t="inlineStr"/>
-      <c r="Q21" s="3" t="inlineStr"/>
-      <c r="R21" s="3" t="inlineStr"/>
-      <c r="S21" s="3" t="inlineStr"/>
-      <c r="T21" s="3" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr"/>
+      <c r="W21" s="2" t="inlineStr"/>
+      <c r="X21" s="2" t="inlineStr"/>
+      <c r="Y21" s="2" t="inlineStr"/>
+      <c r="Z21" s="2" t="inlineStr">
         <is>
           <t>上车 3,000</t>
         </is>
       </c>
-      <c r="U21" s="3" t="inlineStr"/>
-      <c r="V21" s="5" t="n">
+      <c r="AA21" s="2" t="inlineStr"/>
+      <c r="AB21" s="5" t="n">
         <v>3000</v>
       </c>
-      <c r="W21" s="3" t="inlineStr"/>
-      <c r="X21" s="3" t="inlineStr"/>
-      <c r="Y21" s="3" t="inlineStr"/>
-      <c r="Z21" s="3" t="inlineStr"/>
-      <c r="AA21" s="4" t="n">
+      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AD21" s="2" t="inlineStr"/>
+      <c r="AE21" s="2" t="inlineStr"/>
+      <c r="AF21" s="2" t="inlineStr"/>
+      <c r="AG21" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="AB21" s="3" t="inlineStr"/>
-      <c r="AC21" s="3" t="inlineStr"/>
-      <c r="AD21" s="3" t="inlineStr"/>
-      <c r="AE21" s="3" t="inlineStr"/>
+      <c r="AH21" s="2" t="inlineStr"/>
+      <c r="AI21" s="2" t="inlineStr"/>
+      <c r="AJ21" s="2" t="inlineStr"/>
+      <c r="AK21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>c021</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
+          <t>work_tip_01</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
           <t>同事小王</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>tongshi_xiaowang</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>👨‍💼</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>职场</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>我表哥在券商，说最近有个大动作。跟不跟？</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr"/>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>不信小道消息</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr"/>
-      <c r="J22" s="3" t="inlineStr"/>
-      <c r="K22" s="3" t="inlineStr"/>
-      <c r="L22" s="3" t="inlineStr"/>
-      <c r="M22" s="3" t="inlineStr"/>
-      <c r="N22" s="3" t="inlineStr"/>
-      <c r="O22" s="5" t="n">
+      <c r="O22" s="2" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr"/>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P22" s="3" t="inlineStr"/>
-      <c r="Q22" s="3" t="inlineStr"/>
-      <c r="R22" s="3" t="inlineStr"/>
-      <c r="S22" s="3" t="inlineStr"/>
-      <c r="T22" s="3" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr"/>
+      <c r="W22" s="2" t="inlineStr"/>
+      <c r="X22" s="2" t="inlineStr"/>
+      <c r="Y22" s="2" t="inlineStr"/>
+      <c r="Z22" s="2" t="inlineStr">
         <is>
           <t>跟 3,000</t>
         </is>
       </c>
-      <c r="U22" s="3" t="inlineStr"/>
-      <c r="V22" s="5" t="n">
+      <c r="AA22" s="2" t="inlineStr"/>
+      <c r="AB22" s="5" t="n">
         <v>3000</v>
       </c>
-      <c r="W22" s="3" t="inlineStr"/>
-      <c r="X22" s="3" t="inlineStr"/>
-      <c r="Y22" s="3" t="inlineStr"/>
-      <c r="Z22" s="3" t="inlineStr"/>
-      <c r="AA22" s="4" t="n">
+      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AD22" s="2" t="inlineStr"/>
+      <c r="AE22" s="2" t="inlineStr"/>
+      <c r="AF22" s="2" t="inlineStr"/>
+      <c r="AG22" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="AB22" s="5" t="n">
+      <c r="AH22" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="AC22" s="3" t="inlineStr"/>
-      <c r="AD22" s="3" t="inlineStr"/>
-      <c r="AE22" s="3" t="inlineStr"/>
+      <c r="AI22" s="2" t="inlineStr"/>
+      <c r="AJ22" s="2" t="inlineStr"/>
+      <c r="AK22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>c022</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
+          <t>work_overtime_01</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
           <t>项目</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>xiangmu</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>🌃</t>
         </is>
       </c>
-      <c r="D23" s="3" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>职场</t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>今晚上线，全组通宵。你走吗？</t>
         </is>
       </c>
-      <c r="F23" s="3" t="inlineStr"/>
-      <c r="G23" s="3" t="inlineStr"/>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>准时走</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr"/>
-      <c r="J23" s="3" t="inlineStr"/>
-      <c r="K23" s="3" t="inlineStr"/>
-      <c r="L23" s="3" t="inlineStr"/>
-      <c r="M23" s="3" t="inlineStr"/>
-      <c r="N23" s="3" t="inlineStr"/>
-      <c r="O23" s="5" t="n">
+      <c r="O23" s="2" t="inlineStr"/>
+      <c r="P23" s="2" t="inlineStr"/>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P23" s="3" t="inlineStr"/>
-      <c r="Q23" s="4" t="n">
+      <c r="V23" s="2" t="inlineStr"/>
+      <c r="W23" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="R23" s="3" t="inlineStr"/>
-      <c r="S23" s="3" t="inlineStr"/>
-      <c r="T23" s="3" t="inlineStr">
+      <c r="X23" s="2" t="inlineStr"/>
+      <c r="Y23" s="2" t="inlineStr"/>
+      <c r="Z23" s="2" t="inlineStr">
         <is>
           <t>留下来</t>
         </is>
       </c>
-      <c r="U23" s="3" t="inlineStr"/>
-      <c r="V23" s="3" t="inlineStr"/>
-      <c r="W23" s="3" t="inlineStr"/>
-      <c r="X23" s="3" t="inlineStr"/>
-      <c r="Y23" s="3" t="inlineStr"/>
-      <c r="Z23" s="3" t="inlineStr"/>
-      <c r="AA23" s="4" t="n">
+      <c r="AA23" s="2" t="inlineStr"/>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr"/>
+      <c r="AE23" s="2" t="inlineStr"/>
+      <c r="AF23" s="2" t="inlineStr"/>
+      <c r="AG23" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="AB23" s="3" t="inlineStr"/>
-      <c r="AC23" s="5" t="n">
+      <c r="AH23" s="2" t="inlineStr"/>
+      <c r="AI23" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="AD23" s="3" t="inlineStr"/>
-      <c r="AE23" s="3" t="inlineStr"/>
+      <c r="AJ23" s="2" t="inlineStr"/>
+      <c r="AK23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>c023</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
+          <t>inc_salary_01</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
           <t>工资</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>gongzi</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>💵</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>这个月工资到账了。</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>no:fired</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr"/>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>留着过日子</t>
         </is>
       </c>
-      <c r="I24" s="3" t="inlineStr"/>
-      <c r="J24" s="3" t="inlineStr"/>
-      <c r="K24" s="3" t="inlineStr"/>
-      <c r="L24" s="3" t="inlineStr"/>
-      <c r="M24" s="3" t="inlineStr"/>
-      <c r="N24" s="5" t="n">
+      <c r="O24" s="2" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr"/>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="5" t="n">
         <v>6500</v>
       </c>
-      <c r="O24" s="5" t="n">
+      <c r="U24" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P24" s="3" t="inlineStr"/>
-      <c r="Q24" s="3" t="inlineStr"/>
-      <c r="R24" s="3" t="inlineStr"/>
-      <c r="S24" s="3" t="inlineStr"/>
-      <c r="T24" s="3" t="inlineStr">
+      <c r="V24" s="2" t="inlineStr"/>
+      <c r="W24" s="2" t="inlineStr"/>
+      <c r="X24" s="2" t="inlineStr"/>
+      <c r="Y24" s="2" t="inlineStr"/>
+      <c r="Z24" s="2" t="inlineStr">
         <is>
           <t>投进去 5,000</t>
         </is>
       </c>
-      <c r="U24" s="3" t="inlineStr"/>
-      <c r="V24" s="5" t="n">
+      <c r="AA24" s="2" t="inlineStr"/>
+      <c r="AB24" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="W24" s="3" t="inlineStr"/>
-      <c r="X24" s="3" t="inlineStr"/>
-      <c r="Y24" s="3" t="inlineStr"/>
-      <c r="Z24" s="3" t="inlineStr"/>
-      <c r="AA24" s="4" t="n">
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr"/>
+      <c r="AE24" s="2" t="inlineStr"/>
+      <c r="AF24" s="2" t="inlineStr"/>
+      <c r="AG24" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="AB24" s="3" t="inlineStr"/>
-      <c r="AC24" s="3" t="inlineStr"/>
-      <c r="AD24" s="3" t="inlineStr"/>
-      <c r="AE24" s="3" t="inlineStr"/>
+      <c r="AH24" s="2" t="inlineStr"/>
+      <c r="AI24" s="2" t="inlineStr"/>
+      <c r="AJ24" s="2" t="inlineStr"/>
+      <c r="AK24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>c024</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
+          <t>inc_sidejob_01</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
           <t>私活</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>sihuo</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>🧰</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>朋友介绍一个活，做完给 4,000，要占掉两个周末。</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr"/>
-      <c r="G25" s="3" t="inlineStr"/>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>算了</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr"/>
-      <c r="J25" s="3" t="inlineStr"/>
-      <c r="K25" s="3" t="inlineStr"/>
-      <c r="L25" s="3" t="inlineStr"/>
-      <c r="M25" s="3" t="inlineStr"/>
-      <c r="N25" s="3" t="inlineStr"/>
-      <c r="O25" s="5" t="n">
+      <c r="O25" s="2" t="inlineStr"/>
+      <c r="P25" s="2" t="inlineStr"/>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P25" s="3" t="inlineStr"/>
-      <c r="Q25" s="4" t="n">
+      <c r="V25" s="2" t="inlineStr"/>
+      <c r="W25" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="R25" s="3" t="inlineStr"/>
-      <c r="S25" s="3" t="inlineStr"/>
-      <c r="T25" s="3" t="inlineStr">
+      <c r="X25" s="2" t="inlineStr"/>
+      <c r="Y25" s="2" t="inlineStr"/>
+      <c r="Z25" s="2" t="inlineStr">
         <is>
           <t>接了</t>
         </is>
       </c>
-      <c r="U25" s="3" t="inlineStr"/>
-      <c r="V25" s="3" t="inlineStr"/>
-      <c r="W25" s="3" t="inlineStr"/>
-      <c r="X25" s="3" t="inlineStr"/>
-      <c r="Y25" s="3" t="inlineStr"/>
-      <c r="Z25" s="5" t="n">
+      <c r="AA25" s="2" t="inlineStr"/>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr"/>
+      <c r="AE25" s="2" t="inlineStr"/>
+      <c r="AF25" s="5" t="n">
         <v>4000</v>
       </c>
-      <c r="AA25" s="4" t="n">
+      <c r="AG25" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB25" s="3" t="inlineStr"/>
-      <c r="AC25" s="3" t="inlineStr"/>
-      <c r="AD25" s="3" t="inlineStr"/>
-      <c r="AE25" s="3" t="inlineStr"/>
+      <c r="AH25" s="2" t="inlineStr"/>
+      <c r="AI25" s="2" t="inlineStr"/>
+      <c r="AJ25" s="2" t="inlineStr"/>
+      <c r="AK25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>c025</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
+          <t>inc_bonus_01</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
           <t>年终奖</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>nianzhongjiang</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>🧧</t>
         </is>
       </c>
-      <c r="D26" s="3" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>年终奖发了 15,000。</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>no:fired; day&gt;24</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr"/>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>给家里买点东西</t>
         </is>
       </c>
-      <c r="I26" s="5" t="n">
+      <c r="O26" s="5" t="n">
         <v>5200</v>
       </c>
-      <c r="J26" s="3" t="inlineStr"/>
-      <c r="K26" s="3" t="inlineStr"/>
-      <c r="L26" s="3" t="inlineStr"/>
-      <c r="M26" s="3" t="inlineStr"/>
-      <c r="N26" s="3" t="inlineStr"/>
-      <c r="O26" s="5" t="n">
+      <c r="P26" s="2" t="inlineStr"/>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="P26" s="3" t="inlineStr"/>
-      <c r="Q26" s="5" t="n">
+      <c r="V26" s="2" t="inlineStr"/>
+      <c r="W26" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="R26" s="3" t="inlineStr"/>
-      <c r="S26" s="3" t="inlineStr"/>
-      <c r="T26" s="3" t="inlineStr">
+      <c r="X26" s="2" t="inlineStr"/>
+      <c r="Y26" s="2" t="inlineStr"/>
+      <c r="Z26" s="2" t="inlineStr">
         <is>
           <t>全部加仓</t>
         </is>
       </c>
-      <c r="U26" s="3" t="inlineStr"/>
-      <c r="V26" s="5" t="n">
+      <c r="AA26" s="2" t="inlineStr"/>
+      <c r="AB26" s="5" t="n">
         <v>8000</v>
       </c>
-      <c r="W26" s="3" t="inlineStr"/>
-      <c r="X26" s="3" t="inlineStr"/>
-      <c r="Y26" s="3" t="inlineStr"/>
-      <c r="Z26" s="3" t="inlineStr"/>
-      <c r="AA26" s="4" t="n">
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr"/>
+      <c r="AE26" s="2" t="inlineStr"/>
+      <c r="AF26" s="2" t="inlineStr"/>
+      <c r="AG26" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="AB26" s="3" t="inlineStr"/>
-      <c r="AC26" s="3" t="inlineStr"/>
-      <c r="AD26" s="3" t="inlineStr"/>
-      <c r="AE26" s="3" t="inlineStr"/>
+      <c r="AH26" s="2" t="inlineStr"/>
+      <c r="AI26" s="2" t="inlineStr"/>
+      <c r="AJ26" s="2" t="inlineStr"/>
+      <c r="AK26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>c026</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
+          <t>soc_wedding_01</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
           <t>朋友</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>pengyou</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>💌</t>
         </is>
       </c>
-      <c r="D27" s="3" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>人情</t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>我下个月结婚，你知道的。</t>
         </is>
       </c>
-      <c r="F27" s="3" t="inlineStr"/>
-      <c r="G27" s="3" t="inlineStr"/>
-      <c r="H27" s="3" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>装没看见</t>
         </is>
       </c>
-      <c r="I27" s="3" t="inlineStr"/>
-      <c r="J27" s="3" t="inlineStr"/>
-      <c r="K27" s="3" t="inlineStr"/>
-      <c r="L27" s="3" t="inlineStr"/>
-      <c r="M27" s="3" t="inlineStr"/>
-      <c r="N27" s="3" t="inlineStr"/>
-      <c r="O27" s="4" t="n">
+      <c r="O27" s="2" t="inlineStr"/>
+      <c r="P27" s="2" t="inlineStr"/>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="P27" s="3" t="inlineStr"/>
-      <c r="Q27" s="4" t="n">
+      <c r="V27" s="2" t="inlineStr"/>
+      <c r="W27" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="R27" s="3" t="inlineStr"/>
-      <c r="S27" s="3" t="inlineStr"/>
-      <c r="T27" s="3" t="inlineStr">
+      <c r="X27" s="2" t="inlineStr"/>
+      <c r="Y27" s="2" t="inlineStr"/>
+      <c r="Z27" s="2" t="inlineStr">
         <is>
           <t>随 1,600</t>
         </is>
       </c>
-      <c r="U27" s="5" t="n">
+      <c r="AA27" s="5" t="n">
         <v>1600</v>
       </c>
-      <c r="V27" s="3" t="inlineStr"/>
-      <c r="W27" s="3" t="inlineStr"/>
-      <c r="X27" s="3" t="inlineStr"/>
-      <c r="Y27" s="3" t="inlineStr"/>
-      <c r="Z27" s="3" t="inlineStr"/>
-      <c r="AA27" s="4" t="n">
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr"/>
+      <c r="AE27" s="2" t="inlineStr"/>
+      <c r="AF27" s="2" t="inlineStr"/>
+      <c r="AG27" s="4" t="n">
         <v>-1</v>
       </c>
-      <c r="AB27" s="3" t="inlineStr"/>
-      <c r="AC27" s="5" t="n">
+      <c r="AH27" s="2" t="inlineStr"/>
+      <c r="AI27" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AD27" s="3" t="inlineStr"/>
-      <c r="AE27" s="3" t="inlineStr"/>
+      <c r="AJ27" s="2" t="inlineStr"/>
+      <c r="AK27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>c027</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="3" t="inlineStr">
         <is>
+          <t>soc_lend_01</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
           <t>朋友</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>pengyou</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>💌</t>
         </is>
       </c>
-      <c r="D28" s="3" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>人情</t>
         </is>
       </c>
-      <c r="E28" s="3" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>借我两万周转一下，下个月一定还。</t>
         </is>
       </c>
-      <c r="F28" s="3" t="inlineStr"/>
-      <c r="G28" s="3" t="inlineStr"/>
-      <c r="H28" s="3" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>说自己也紧</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr"/>
-      <c r="J28" s="3" t="inlineStr"/>
-      <c r="K28" s="3" t="inlineStr"/>
-      <c r="L28" s="3" t="inlineStr"/>
-      <c r="M28" s="3" t="inlineStr"/>
-      <c r="N28" s="3" t="inlineStr"/>
-      <c r="O28" s="4" t="n">
+      <c r="O28" s="2" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr"/>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="P28" s="3" t="inlineStr"/>
-      <c r="Q28" s="4" t="n">
+      <c r="V28" s="2" t="inlineStr"/>
+      <c r="W28" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="R28" s="3" t="inlineStr"/>
-      <c r="S28" s="3" t="inlineStr"/>
-      <c r="T28" s="3" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr"/>
+      <c r="Y28" s="2" t="inlineStr"/>
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>借他 3,900</t>
         </is>
       </c>
-      <c r="U28" s="5" t="n">
+      <c r="AA28" s="5" t="n">
         <v>3900</v>
       </c>
-      <c r="V28" s="3" t="inlineStr"/>
-      <c r="W28" s="3" t="inlineStr"/>
-      <c r="X28" s="3" t="inlineStr"/>
-      <c r="Y28" s="3" t="inlineStr"/>
-      <c r="Z28" s="3" t="inlineStr"/>
-      <c r="AA28" s="4" t="n">
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr"/>
+      <c r="AE28" s="2" t="inlineStr"/>
+      <c r="AF28" s="2" t="inlineStr"/>
+      <c r="AG28" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="AB28" s="3" t="inlineStr"/>
-      <c r="AC28" s="5" t="n">
+      <c r="AH28" s="2" t="inlineStr"/>
+      <c r="AI28" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AD28" s="3" t="inlineStr"/>
-      <c r="AE28" s="3" t="inlineStr"/>
+      <c r="AJ28" s="2" t="inlineStr"/>
+      <c r="AK28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>c028</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
+          <t>soc_reunion_01</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
           <t>同学</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>tongxue</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>🍻</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>人情</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t>老同学聚会，人均 600。听说你最近在做投资？</t>
         </is>
       </c>
-      <c r="F29" s="3" t="inlineStr"/>
-      <c r="G29" s="3" t="inlineStr"/>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>不去</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr"/>
-      <c r="J29" s="3" t="inlineStr"/>
-      <c r="K29" s="3" t="inlineStr"/>
-      <c r="L29" s="3" t="inlineStr"/>
-      <c r="M29" s="3" t="inlineStr"/>
-      <c r="N29" s="3" t="inlineStr"/>
-      <c r="O29" s="4" t="n">
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr"/>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="P29" s="3" t="inlineStr"/>
-      <c r="Q29" s="4" t="n">
+      <c r="V29" s="2" t="inlineStr"/>
+      <c r="W29" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="R29" s="3" t="inlineStr"/>
-      <c r="S29" s="3" t="inlineStr"/>
-      <c r="T29" s="3" t="inlineStr">
+      <c r="X29" s="2" t="inlineStr"/>
+      <c r="Y29" s="2" t="inlineStr"/>
+      <c r="Z29" s="2" t="inlineStr">
         <is>
           <t>去，AA 也行</t>
         </is>
       </c>
-      <c r="U29" s="5" t="n">
+      <c r="AA29" s="5" t="n">
         <v>1600</v>
       </c>
-      <c r="V29" s="3" t="inlineStr"/>
-      <c r="W29" s="3" t="inlineStr"/>
-      <c r="X29" s="3" t="inlineStr"/>
-      <c r="Y29" s="3" t="inlineStr"/>
-      <c r="Z29" s="3" t="inlineStr"/>
-      <c r="AA29" s="5" t="n">
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr"/>
+      <c r="AE29" s="2" t="inlineStr"/>
+      <c r="AF29" s="2" t="inlineStr"/>
+      <c r="AG29" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="AB29" s="3" t="inlineStr"/>
-      <c r="AC29" s="5" t="n">
+      <c r="AH29" s="2" t="inlineStr"/>
+      <c r="AI29" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="AD29" s="3" t="inlineStr"/>
-      <c r="AE29" s="3" t="inlineStr"/>
+      <c r="AJ29" s="2" t="inlineStr"/>
+      <c r="AK29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>c029</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
+          <t>soc_banquet_01</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
           <t>张阿姨</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>zhangayi</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>🏘</t>
         </is>
       </c>
-      <c r="D30" s="3" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>人情</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>楼下办寿宴，整栋楼都去了。</t>
         </is>
       </c>
-      <c r="F30" s="3" t="inlineStr"/>
-      <c r="G30" s="3" t="inlineStr"/>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>装不在家</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr"/>
-      <c r="J30" s="3" t="inlineStr"/>
-      <c r="K30" s="3" t="inlineStr"/>
-      <c r="L30" s="3" t="inlineStr"/>
-      <c r="M30" s="3" t="inlineStr"/>
-      <c r="N30" s="3" t="inlineStr"/>
-      <c r="O30" s="3" t="inlineStr"/>
-      <c r="P30" s="3" t="inlineStr"/>
-      <c r="Q30" s="4" t="n">
+      <c r="O30" s="2" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr"/>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr"/>
+      <c r="W30" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="R30" s="3" t="inlineStr"/>
-      <c r="S30" s="3" t="inlineStr"/>
-      <c r="T30" s="3" t="inlineStr">
+      <c r="X30" s="2" t="inlineStr"/>
+      <c r="Y30" s="2" t="inlineStr"/>
+      <c r="Z30" s="2" t="inlineStr">
         <is>
           <t>随 800</t>
         </is>
       </c>
-      <c r="U30" s="5" t="n">
+      <c r="AA30" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="V30" s="3" t="inlineStr"/>
-      <c r="W30" s="3" t="inlineStr"/>
-      <c r="X30" s="3" t="inlineStr"/>
-      <c r="Y30" s="3" t="inlineStr"/>
-      <c r="Z30" s="3" t="inlineStr"/>
-      <c r="AA30" s="3" t="inlineStr"/>
-      <c r="AB30" s="3" t="inlineStr"/>
-      <c r="AC30" s="5" t="n">
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr"/>
+      <c r="AE30" s="2" t="inlineStr"/>
+      <c r="AF30" s="2" t="inlineStr"/>
+      <c r="AG30" s="2" t="inlineStr"/>
+      <c r="AH30" s="2" t="inlineStr"/>
+      <c r="AI30" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="AD30" s="3" t="inlineStr"/>
-      <c r="AE30" s="3" t="inlineStr"/>
+      <c r="AJ30" s="2" t="inlineStr"/>
+      <c r="AK30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>c030</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
+          <t>soc_scam_01</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
           <t>老同学</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>laotongxue</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>🤳</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>人情</t>
         </is>
       </c>
-      <c r="E31" s="3" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>有个项目，稳赚，就是得先投点钱。</t>
         </is>
       </c>
-      <c r="F31" s="3" t="inlineStr">
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>social&gt;48</t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr"/>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>算了</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr"/>
-      <c r="J31" s="3" t="inlineStr"/>
-      <c r="K31" s="3" t="inlineStr"/>
-      <c r="L31" s="3" t="inlineStr"/>
-      <c r="M31" s="3" t="inlineStr"/>
-      <c r="N31" s="3" t="inlineStr"/>
-      <c r="O31" s="5" t="n">
+      <c r="O31" s="2" t="inlineStr"/>
+      <c r="P31" s="2" t="inlineStr"/>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="P31" s="3" t="inlineStr"/>
-      <c r="Q31" s="4" t="n">
+      <c r="V31" s="2" t="inlineStr"/>
+      <c r="W31" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="R31" s="3" t="inlineStr"/>
-      <c r="S31" s="3" t="inlineStr"/>
-      <c r="T31" s="3" t="inlineStr">
+      <c r="X31" s="2" t="inlineStr"/>
+      <c r="Y31" s="2" t="inlineStr"/>
+      <c r="Z31" s="2" t="inlineStr">
         <is>
           <t>投 6,500</t>
         </is>
       </c>
-      <c r="U31" s="5" t="n">
+      <c r="AA31" s="5" t="n">
         <v>6500</v>
       </c>
-      <c r="V31" s="3" t="inlineStr"/>
-      <c r="W31" s="3" t="inlineStr"/>
-      <c r="X31" s="3" t="inlineStr"/>
-      <c r="Y31" s="3" t="inlineStr"/>
-      <c r="Z31" s="3" t="inlineStr"/>
-      <c r="AA31" s="4" t="n">
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr"/>
+      <c r="AE31" s="2" t="inlineStr"/>
+      <c r="AF31" s="2" t="inlineStr"/>
+      <c r="AG31" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB31" s="5" t="n">
+      <c r="AH31" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="AC31" s="5" t="n">
+      <c r="AI31" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="AD31" s="3" t="inlineStr"/>
-      <c r="AE31" s="3" t="inlineStr"/>
+      <c r="AJ31" s="2" t="inlineStr"/>
+      <c r="AK31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>c031</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="3" t="inlineStr">
         <is>
+          <t>soc_whisper_01</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
           <t>饭局</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>fanju</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>🥢</t>
         </is>
       </c>
-      <c r="D32" s="3" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>人情</t>
         </is>
       </c>
-      <c r="E32" s="3" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>有人凑到你耳边说了几句，就几句。</t>
         </is>
       </c>
-      <c r="F32" s="3" t="inlineStr">
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>no:insider; social&gt;45</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr"/>
-      <c r="H32" s="3" t="inlineStr">
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>当没听见</t>
         </is>
       </c>
-      <c r="I32" s="3" t="inlineStr"/>
-      <c r="J32" s="3" t="inlineStr"/>
-      <c r="K32" s="3" t="inlineStr"/>
-      <c r="L32" s="3" t="inlineStr"/>
-      <c r="M32" s="3" t="inlineStr"/>
-      <c r="N32" s="3" t="inlineStr"/>
-      <c r="O32" s="5" t="n">
+      <c r="O32" s="2" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr"/>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="P32" s="3" t="inlineStr"/>
-      <c r="Q32" s="3" t="inlineStr"/>
-      <c r="R32" s="3" t="inlineStr"/>
-      <c r="S32" s="3" t="inlineStr"/>
-      <c r="T32" s="3" t="inlineStr">
+      <c r="V32" s="2" t="inlineStr"/>
+      <c r="W32" s="2" t="inlineStr"/>
+      <c r="X32" s="2" t="inlineStr"/>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr">
         <is>
           <t>记住这个消息</t>
         </is>
       </c>
-      <c r="U32" s="3" t="inlineStr"/>
-      <c r="V32" s="3" t="inlineStr"/>
-      <c r="W32" s="3" t="inlineStr"/>
-      <c r="X32" s="3" t="inlineStr"/>
-      <c r="Y32" s="3" t="inlineStr"/>
-      <c r="Z32" s="3" t="inlineStr"/>
-      <c r="AA32" s="4" t="n">
+      <c r="AA32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr"/>
+      <c r="AE32" s="2" t="inlineStr"/>
+      <c r="AF32" s="2" t="inlineStr"/>
+      <c r="AG32" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="AB32" s="5" t="n">
+      <c r="AH32" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="AC32" s="3" t="inlineStr"/>
-      <c r="AD32" s="3" t="inlineStr">
+      <c r="AI32" s="2" t="inlineStr"/>
+      <c r="AJ32" s="2" t="inlineStr">
         <is>
           <t>insider:6</t>
         </is>
       </c>
-      <c r="AE32" s="3" t="inlineStr"/>
+      <c r="AK32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>c032</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="3" t="inlineStr">
         <is>
+          <t>self_checkup_01</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
           <t>体检报告</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>tijian</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>🏥</t>
         </is>
       </c>
-      <c r="D33" s="3" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>自己</t>
         </is>
       </c>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>血压偏高，熬夜太多。医生让你少盯屏幕。</t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
         <is>
           <t>今晚不看了</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr"/>
-      <c r="J33" s="3" t="inlineStr"/>
-      <c r="K33" s="3" t="inlineStr"/>
-      <c r="L33" s="3" t="inlineStr"/>
-      <c r="M33" s="3" t="inlineStr"/>
-      <c r="N33" s="3" t="inlineStr"/>
-      <c r="O33" s="5" t="n">
+      <c r="O33" s="2" t="inlineStr"/>
+      <c r="P33" s="2" t="inlineStr"/>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="P33" s="3" t="inlineStr"/>
-      <c r="Q33" s="3" t="inlineStr"/>
-      <c r="R33" s="3" t="inlineStr"/>
-      <c r="S33" s="3" t="inlineStr"/>
-      <c r="T33" s="3" t="inlineStr">
+      <c r="V33" s="2" t="inlineStr"/>
+      <c r="W33" s="2" t="inlineStr"/>
+      <c r="X33" s="2" t="inlineStr"/>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr">
         <is>
           <t>没事，我扛得住</t>
         </is>
       </c>
-      <c r="U33" s="3" t="inlineStr"/>
-      <c r="V33" s="3" t="inlineStr"/>
-      <c r="W33" s="3" t="inlineStr"/>
-      <c r="X33" s="3" t="inlineStr"/>
-      <c r="Y33" s="3" t="inlineStr"/>
-      <c r="Z33" s="3" t="inlineStr"/>
-      <c r="AA33" s="4" t="n">
+      <c r="AA33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr"/>
+      <c r="AE33" s="2" t="inlineStr"/>
+      <c r="AF33" s="2" t="inlineStr"/>
+      <c r="AG33" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="AB33" s="3" t="inlineStr"/>
-      <c r="AC33" s="3" t="inlineStr"/>
-      <c r="AD33" s="3" t="inlineStr"/>
-      <c r="AE33" s="3" t="inlineStr"/>
+      <c r="AH33" s="2" t="inlineStr"/>
+      <c r="AI33" s="2" t="inlineStr"/>
+      <c r="AJ33" s="2" t="inlineStr"/>
+      <c r="AK33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>c033</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="3" t="inlineStr">
         <is>
+          <t>self_night_01</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
           <t>凌晨三点</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>lingsan</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>🌙</t>
         </is>
       </c>
-      <c r="D34" s="3" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>自己</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>你还没睡。屏幕的蓝光里，那根线还在跳。</t>
         </is>
       </c>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>睡了</t>
         </is>
       </c>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="3" t="inlineStr"/>
-      <c r="K34" s="3" t="inlineStr"/>
-      <c r="L34" s="3" t="inlineStr"/>
-      <c r="M34" s="3" t="inlineStr"/>
-      <c r="N34" s="3" t="inlineStr"/>
-      <c r="O34" s="5" t="n">
+      <c r="O34" s="2" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr"/>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="P34" s="3" t="inlineStr"/>
-      <c r="Q34" s="3" t="inlineStr"/>
-      <c r="R34" s="3" t="inlineStr"/>
-      <c r="S34" s="3" t="inlineStr"/>
-      <c r="T34" s="3" t="inlineStr">
+      <c r="V34" s="2" t="inlineStr"/>
+      <c r="W34" s="2" t="inlineStr"/>
+      <c r="X34" s="2" t="inlineStr"/>
+      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr">
         <is>
           <t>再看五分钟</t>
         </is>
       </c>
-      <c r="U34" s="3" t="inlineStr"/>
-      <c r="V34" s="3" t="inlineStr"/>
-      <c r="W34" s="3" t="inlineStr"/>
-      <c r="X34" s="3" t="inlineStr"/>
-      <c r="Y34" s="3" t="inlineStr"/>
-      <c r="Z34" s="3" t="inlineStr"/>
-      <c r="AA34" s="4" t="n">
+      <c r="AA34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr"/>
+      <c r="AE34" s="2" t="inlineStr"/>
+      <c r="AF34" s="2" t="inlineStr"/>
+      <c r="AG34" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB34" s="5" t="n">
+      <c r="AH34" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="AC34" s="3" t="inlineStr"/>
-      <c r="AD34" s="3" t="inlineStr"/>
-      <c r="AE34" s="3" t="inlineStr"/>
+      <c r="AI34" s="2" t="inlineStr"/>
+      <c r="AJ34" s="2" t="inlineStr"/>
+      <c r="AK34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>c034</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="3" t="inlineStr">
         <is>
+          <t>self_mirror_01</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
           <t>镜子</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>jingzi</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>🪞</t>
         </is>
       </c>
-      <c r="D35" s="3" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>自己</t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t>你盯着屏幕，忽然问自己：我到底在干什么？</t>
         </is>
       </c>
-      <c r="F35" s="3" t="inlineStr"/>
-      <c r="G35" s="3" t="inlineStr"/>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M35" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>……不知道</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr"/>
-      <c r="J35" s="3" t="inlineStr"/>
-      <c r="K35" s="3" t="inlineStr"/>
-      <c r="L35" s="3" t="inlineStr"/>
-      <c r="M35" s="3" t="inlineStr"/>
-      <c r="N35" s="3" t="inlineStr"/>
-      <c r="O35" s="4" t="n">
+      <c r="O35" s="2" t="inlineStr"/>
+      <c r="P35" s="2" t="inlineStr"/>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="P35" s="3" t="inlineStr"/>
-      <c r="Q35" s="3" t="inlineStr"/>
-      <c r="R35" s="3" t="inlineStr"/>
-      <c r="S35" s="3" t="inlineStr"/>
-      <c r="T35" s="3" t="inlineStr">
+      <c r="V35" s="2" t="inlineStr"/>
+      <c r="W35" s="2" t="inlineStr"/>
+      <c r="X35" s="2" t="inlineStr"/>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr">
         <is>
           <t>为了自由</t>
         </is>
       </c>
-      <c r="U35" s="3" t="inlineStr"/>
-      <c r="V35" s="3" t="inlineStr"/>
-      <c r="W35" s="3" t="inlineStr"/>
-      <c r="X35" s="3" t="inlineStr"/>
-      <c r="Y35" s="3" t="inlineStr"/>
-      <c r="Z35" s="3" t="inlineStr"/>
-      <c r="AA35" s="5" t="n">
+      <c r="AA35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr"/>
+      <c r="AE35" s="2" t="inlineStr"/>
+      <c r="AF35" s="2" t="inlineStr"/>
+      <c r="AG35" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="AB35" s="3" t="inlineStr"/>
-      <c r="AC35" s="3" t="inlineStr"/>
-      <c r="AD35" s="3" t="inlineStr"/>
-      <c r="AE35" s="3" t="inlineStr"/>
+      <c r="AH35" s="2" t="inlineStr"/>
+      <c r="AI35" s="2" t="inlineStr"/>
+      <c r="AJ35" s="2" t="inlineStr"/>
+      <c r="AK35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>c035</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="3" t="inlineStr">
         <is>
+          <t>self_weekend_01</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
           <t>周末</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>zhoumo</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>🌿</t>
         </is>
       </c>
-      <c r="D36" s="3" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>自己</t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>难得一个完整的周末，没人找你，也没什么消息。</t>
         </is>
       </c>
-      <c r="F36" s="3" t="inlineStr"/>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr">
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M36" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
         <is>
           <t>带家人出去走走</t>
         </is>
       </c>
-      <c r="I36" s="5" t="n">
+      <c r="O36" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="J36" s="3" t="inlineStr"/>
-      <c r="K36" s="3" t="inlineStr"/>
-      <c r="L36" s="3" t="inlineStr"/>
-      <c r="M36" s="3" t="inlineStr"/>
-      <c r="N36" s="3" t="inlineStr"/>
-      <c r="O36" s="5" t="n">
+      <c r="P36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="P36" s="3" t="inlineStr"/>
-      <c r="Q36" s="5" t="n">
+      <c r="V36" s="2" t="inlineStr"/>
+      <c r="W36" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="R36" s="3" t="inlineStr"/>
-      <c r="S36" s="3" t="inlineStr"/>
-      <c r="T36" s="3" t="inlineStr">
+      <c r="X36" s="2" t="inlineStr"/>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr">
         <is>
           <t>研究一下行情</t>
         </is>
       </c>
-      <c r="U36" s="3" t="inlineStr"/>
-      <c r="V36" s="3" t="inlineStr"/>
-      <c r="W36" s="3" t="inlineStr"/>
-      <c r="X36" s="3" t="inlineStr"/>
-      <c r="Y36" s="3" t="inlineStr"/>
-      <c r="Z36" s="3" t="inlineStr"/>
-      <c r="AA36" s="4" t="n">
+      <c r="AA36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr"/>
+      <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="inlineStr"/>
+      <c r="AG36" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="AB36" s="3" t="inlineStr"/>
-      <c r="AC36" s="3" t="inlineStr"/>
-      <c r="AD36" s="3" t="inlineStr"/>
-      <c r="AE36" s="3" t="inlineStr"/>
+      <c r="AH36" s="2" t="inlineStr"/>
+      <c r="AI36" s="2" t="inlineStr"/>
+      <c r="AJ36" s="2" t="inlineStr"/>
+      <c r="AK36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>c036</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="3" t="inlineStr">
         <is>
+          <t>self_hairloss_01</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
           <t>地漏</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>dilou</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>🚿</t>
         </is>
       </c>
-      <c r="D37" s="3" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>自己</t>
         </is>
       </c>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t>洗完头，地漏上是一层头发。</t>
         </is>
       </c>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr">
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M37" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
         <is>
           <t>去挂个号</t>
         </is>
       </c>
-      <c r="I37" s="5" t="n">
+      <c r="O37" s="5" t="n">
         <v>1600</v>
       </c>
-      <c r="J37" s="3" t="inlineStr"/>
-      <c r="K37" s="3" t="inlineStr"/>
-      <c r="L37" s="3" t="inlineStr"/>
-      <c r="M37" s="3" t="inlineStr"/>
-      <c r="N37" s="3" t="inlineStr"/>
-      <c r="O37" s="5" t="n">
+      <c r="P37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="P37" s="3" t="inlineStr"/>
-      <c r="Q37" s="3" t="inlineStr"/>
-      <c r="R37" s="3" t="inlineStr"/>
-      <c r="S37" s="3" t="inlineStr"/>
-      <c r="T37" s="3" t="inlineStr">
+      <c r="V37" s="2" t="inlineStr"/>
+      <c r="W37" s="2" t="inlineStr"/>
+      <c r="X37" s="2" t="inlineStr"/>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr">
         <is>
           <t>没事</t>
         </is>
       </c>
-      <c r="U37" s="3" t="inlineStr"/>
-      <c r="V37" s="3" t="inlineStr"/>
-      <c r="W37" s="3" t="inlineStr"/>
-      <c r="X37" s="3" t="inlineStr"/>
-      <c r="Y37" s="3" t="inlineStr"/>
-      <c r="Z37" s="3" t="inlineStr"/>
-      <c r="AA37" s="4" t="n">
+      <c r="AA37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr"/>
+      <c r="AE37" s="2" t="inlineStr"/>
+      <c r="AF37" s="2" t="inlineStr"/>
+      <c r="AG37" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="AB37" s="3" t="inlineStr"/>
-      <c r="AC37" s="3" t="inlineStr"/>
-      <c r="AD37" s="3" t="inlineStr"/>
-      <c r="AE37" s="3" t="inlineStr"/>
+      <c r="AH37" s="2" t="inlineStr"/>
+      <c r="AI37" s="2" t="inlineStr"/>
+      <c r="AJ37" s="2" t="inlineStr"/>
+      <c r="AK37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>c037</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="3" t="inlineStr">
         <is>
+          <t>self_birthday_01</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
           <t>生日</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>shengri</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>🎂</t>
         </is>
       </c>
-      <c r="D38" s="3" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>自己</t>
         </is>
       </c>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>今天你生日。没有人记得。</t>
         </is>
       </c>
-      <c r="F38" s="3" t="inlineStr">
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>social&lt;36</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr"/>
-      <c r="H38" s="3" t="inlineStr">
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M38" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>照常过</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr"/>
-      <c r="J38" s="3" t="inlineStr"/>
-      <c r="K38" s="3" t="inlineStr"/>
-      <c r="L38" s="3" t="inlineStr"/>
-      <c r="M38" s="3" t="inlineStr"/>
-      <c r="N38" s="3" t="inlineStr"/>
-      <c r="O38" s="4" t="n">
+      <c r="O38" s="2" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="4" t="n">
         <v>-7</v>
       </c>
-      <c r="P38" s="3" t="inlineStr"/>
-      <c r="Q38" s="3" t="inlineStr"/>
-      <c r="R38" s="3" t="inlineStr"/>
-      <c r="S38" s="3" t="inlineStr"/>
-      <c r="T38" s="3" t="inlineStr">
+      <c r="V38" s="2" t="inlineStr"/>
+      <c r="W38" s="2" t="inlineStr"/>
+      <c r="X38" s="2" t="inlineStr"/>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr">
         <is>
           <t>给自己买点东西</t>
         </is>
       </c>
-      <c r="U38" s="5" t="n">
+      <c r="AA38" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="V38" s="3" t="inlineStr"/>
-      <c r="W38" s="3" t="inlineStr"/>
-      <c r="X38" s="3" t="inlineStr"/>
-      <c r="Y38" s="3" t="inlineStr"/>
-      <c r="Z38" s="3" t="inlineStr"/>
-      <c r="AA38" s="5" t="n">
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr"/>
+      <c r="AE38" s="2" t="inlineStr"/>
+      <c r="AF38" s="2" t="inlineStr"/>
+      <c r="AG38" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AB38" s="3" t="inlineStr"/>
-      <c r="AC38" s="3" t="inlineStr"/>
-      <c r="AD38" s="3" t="inlineStr"/>
-      <c r="AE38" s="3" t="inlineStr"/>
+      <c r="AH38" s="2" t="inlineStr"/>
+      <c r="AI38" s="2" t="inlineStr"/>
+      <c r="AJ38" s="2" t="inlineStr"/>
+      <c r="AK38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>c038</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="3" t="inlineStr">
         <is>
+          <t>mkt_easing_01</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
           <t>银行</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>yinhang</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>🏦</t>
         </is>
       </c>
-      <c r="D39" s="3" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>市场</t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>新闻说银行要放水了，市面上的钱会变多。</t>
         </is>
       </c>
-      <c r="F39" s="3" t="inlineStr"/>
-      <c r="G39" s="3" t="inlineStr"/>
-      <c r="H39" s="3" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M39" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
         <is>
           <t>听过太多次了</t>
         </is>
       </c>
-      <c r="I39" s="3" t="inlineStr"/>
-      <c r="J39" s="3" t="inlineStr"/>
-      <c r="K39" s="3" t="inlineStr"/>
-      <c r="L39" s="3" t="inlineStr"/>
-      <c r="M39" s="3" t="inlineStr"/>
-      <c r="N39" s="3" t="inlineStr"/>
-      <c r="O39" s="5" t="n">
+      <c r="O39" s="2" t="inlineStr"/>
+      <c r="P39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P39" s="3" t="inlineStr"/>
-      <c r="Q39" s="3" t="inlineStr"/>
-      <c r="R39" s="3" t="inlineStr"/>
-      <c r="S39" s="3" t="inlineStr"/>
-      <c r="T39" s="3" t="inlineStr">
+      <c r="V39" s="2" t="inlineStr"/>
+      <c r="W39" s="2" t="inlineStr"/>
+      <c r="X39" s="2" t="inlineStr"/>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr">
         <is>
           <t>加仓 3,000</t>
         </is>
       </c>
-      <c r="U39" s="3" t="inlineStr"/>
-      <c r="V39" s="5" t="n">
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="5" t="n">
         <v>3000</v>
       </c>
-      <c r="W39" s="3" t="inlineStr"/>
-      <c r="X39" s="3" t="inlineStr"/>
-      <c r="Y39" s="3" t="inlineStr"/>
-      <c r="Z39" s="3" t="inlineStr"/>
-      <c r="AA39" s="4" t="n">
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr"/>
+      <c r="AE39" s="2" t="inlineStr"/>
+      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AG39" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="AB39" s="3" t="inlineStr"/>
-      <c r="AC39" s="3" t="inlineStr"/>
-      <c r="AD39" s="3" t="inlineStr"/>
-      <c r="AE39" s="3" t="inlineStr"/>
+      <c r="AH39" s="2" t="inlineStr"/>
+      <c r="AI39" s="2" t="inlineStr"/>
+      <c r="AJ39" s="2" t="inlineStr"/>
+      <c r="AK39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>c039</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="3" t="inlineStr">
         <is>
+          <t>mkt_macro_01</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
           <t>新闻</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>xinwen</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>🌐</t>
         </is>
       </c>
-      <c r="D40" s="3" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>市场</t>
         </is>
       </c>
-      <c r="E40" s="3" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr">
         <is>
           <t>美国那边利息涨了，据说全球的钱都在往回跑。</t>
         </is>
       </c>
-      <c r="F40" s="3" t="inlineStr"/>
-      <c r="G40" s="3" t="inlineStr"/>
-      <c r="H40" s="3" t="inlineStr">
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M40" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
         <is>
           <t>先看看</t>
         </is>
       </c>
-      <c r="I40" s="3" t="inlineStr"/>
-      <c r="J40" s="3" t="inlineStr"/>
-      <c r="K40" s="5" t="n">
+      <c r="O40" s="2" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr"/>
+      <c r="Q40" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="L40" s="3" t="inlineStr"/>
-      <c r="M40" s="3" t="inlineStr"/>
-      <c r="N40" s="3" t="inlineStr"/>
-      <c r="O40" s="5" t="n">
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P40" s="3" t="inlineStr"/>
-      <c r="Q40" s="3" t="inlineStr"/>
-      <c r="R40" s="3" t="inlineStr"/>
-      <c r="S40" s="3" t="inlineStr"/>
-      <c r="T40" s="3" t="inlineStr">
+      <c r="V40" s="2" t="inlineStr"/>
+      <c r="W40" s="2" t="inlineStr"/>
+      <c r="X40" s="2" t="inlineStr"/>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr">
         <is>
           <t>抄底 2,000</t>
         </is>
       </c>
-      <c r="U40" s="3" t="inlineStr"/>
-      <c r="V40" s="5" t="n">
+      <c r="AA40" s="2" t="inlineStr"/>
+      <c r="AB40" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="W40" s="3" t="inlineStr"/>
-      <c r="X40" s="3" t="inlineStr"/>
-      <c r="Y40" s="3" t="inlineStr"/>
-      <c r="Z40" s="3" t="inlineStr"/>
-      <c r="AA40" s="4" t="n">
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr"/>
+      <c r="AE40" s="2" t="inlineStr"/>
+      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AG40" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="AB40" s="3" t="inlineStr"/>
-      <c r="AC40" s="3" t="inlineStr"/>
-      <c r="AD40" s="3" t="inlineStr"/>
-      <c r="AE40" s="3" t="inlineStr"/>
+      <c r="AH40" s="2" t="inlineStr"/>
+      <c r="AI40" s="2" t="inlineStr"/>
+      <c r="AJ40" s="2" t="inlineStr"/>
+      <c r="AK40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>c040</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="3" t="inlineStr">
         <is>
+          <t>mkt_policy_01</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
           <t>新闻联播</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>xinwenlianbo</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>📺</t>
         </is>
       </c>
-      <c r="D41" s="3" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>市场</t>
         </is>
       </c>
-      <c r="E41" s="3" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr">
         <is>
           <t>要活跃资本市场，提振投资者信心。</t>
         </is>
       </c>
-      <c r="F41" s="3" t="inlineStr"/>
-      <c r="G41" s="3" t="inlineStr"/>
-      <c r="H41" s="3" t="inlineStr">
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M41" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
         <is>
           <t>政策底不是市场底</t>
         </is>
       </c>
-      <c r="I41" s="3" t="inlineStr"/>
-      <c r="J41" s="3" t="inlineStr"/>
-      <c r="K41" s="3" t="inlineStr"/>
-      <c r="L41" s="3" t="inlineStr"/>
-      <c r="M41" s="3" t="inlineStr"/>
-      <c r="N41" s="3" t="inlineStr"/>
-      <c r="O41" s="5" t="n">
+      <c r="O41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="P41" s="3" t="inlineStr"/>
-      <c r="Q41" s="3" t="inlineStr"/>
-      <c r="R41" s="3" t="inlineStr"/>
-      <c r="S41" s="3" t="inlineStr"/>
-      <c r="T41" s="3" t="inlineStr">
+      <c r="V41" s="2" t="inlineStr"/>
+      <c r="W41" s="2" t="inlineStr"/>
+      <c r="X41" s="2" t="inlineStr"/>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr">
         <is>
           <t>加仓 4,000</t>
         </is>
       </c>
-      <c r="U41" s="3" t="inlineStr"/>
-      <c r="V41" s="5" t="n">
+      <c r="AA41" s="2" t="inlineStr"/>
+      <c r="AB41" s="5" t="n">
         <v>4000</v>
       </c>
-      <c r="W41" s="3" t="inlineStr"/>
-      <c r="X41" s="3" t="inlineStr"/>
-      <c r="Y41" s="3" t="inlineStr"/>
-      <c r="Z41" s="3" t="inlineStr"/>
-      <c r="AA41" s="4" t="n">
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr"/>
+      <c r="AE41" s="2" t="inlineStr"/>
+      <c r="AF41" s="2" t="inlineStr"/>
+      <c r="AG41" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="AB41" s="3" t="inlineStr"/>
-      <c r="AC41" s="3" t="inlineStr"/>
-      <c r="AD41" s="3" t="inlineStr"/>
-      <c r="AE41" s="3" t="inlineStr"/>
+      <c r="AH41" s="2" t="inlineStr"/>
+      <c r="AI41" s="2" t="inlineStr"/>
+      <c r="AJ41" s="2" t="inlineStr"/>
+      <c r="AK41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>c041</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="3" t="inlineStr">
         <is>
+          <t>mkt_earnings_01</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
           <t>公司公告</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>gongsi_gonggao</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>⚠️</t>
         </is>
       </c>
-      <c r="D42" s="3" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>市场</t>
         </is>
       </c>
-      <c r="E42" s="3" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr">
         <is>
           <t>你持有的这家公司说，今年赚的钱少了九成。</t>
         </is>
       </c>
-      <c r="F42" s="3" t="inlineStr">
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>equity&gt;500</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr"/>
-      <c r="H42" s="3" t="inlineStr">
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M42" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
         <is>
           <t>卖一半</t>
         </is>
       </c>
-      <c r="I42" s="3" t="inlineStr"/>
-      <c r="J42" s="3" t="inlineStr"/>
-      <c r="K42" s="5" t="n">
+      <c r="O42" s="2" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr"/>
+      <c r="Q42" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="L42" s="3" t="inlineStr"/>
-      <c r="M42" s="3" t="inlineStr"/>
-      <c r="N42" s="3" t="inlineStr"/>
-      <c r="O42" s="4" t="n">
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="P42" s="3" t="inlineStr"/>
-      <c r="Q42" s="3" t="inlineStr"/>
-      <c r="R42" s="3" t="inlineStr"/>
-      <c r="S42" s="3" t="inlineStr"/>
-      <c r="T42" s="3" t="inlineStr">
+      <c r="V42" s="2" t="inlineStr"/>
+      <c r="W42" s="2" t="inlineStr"/>
+      <c r="X42" s="2" t="inlineStr"/>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr">
         <is>
           <t>补仓摊薄成本</t>
         </is>
       </c>
-      <c r="U42" s="3" t="inlineStr"/>
-      <c r="V42" s="5" t="n">
+      <c r="AA42" s="2" t="inlineStr"/>
+      <c r="AB42" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="W42" s="3" t="inlineStr"/>
-      <c r="X42" s="3" t="inlineStr"/>
-      <c r="Y42" s="3" t="inlineStr"/>
-      <c r="Z42" s="3" t="inlineStr"/>
-      <c r="AA42" s="4" t="n">
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr"/>
+      <c r="AE42" s="2" t="inlineStr"/>
+      <c r="AF42" s="2" t="inlineStr"/>
+      <c r="AG42" s="4" t="n">
         <v>-7</v>
       </c>
-      <c r="AB42" s="3" t="inlineStr"/>
-      <c r="AC42" s="3" t="inlineStr"/>
-      <c r="AD42" s="3" t="inlineStr"/>
-      <c r="AE42" s="3" t="inlineStr"/>
+      <c r="AH42" s="2" t="inlineStr"/>
+      <c r="AI42" s="2" t="inlineStr"/>
+      <c r="AJ42" s="2" t="inlineStr"/>
+      <c r="AK42" s="2" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>c042</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="3" t="inlineStr">
         <is>
+          <t>mkt_insidersell_01</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
           <t>公司公告</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>gongsi_gonggao</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>📉</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>市场</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr">
         <is>
           <t>公司老板自己在卖股票，卖了不少。</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>equity&gt;500</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M43" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
         <is>
           <t>跟着卖一半</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="3" t="inlineStr"/>
-      <c r="K43" s="5" t="n">
+      <c r="O43" s="2" t="inlineStr"/>
+      <c r="P43" s="2" t="inlineStr"/>
+      <c r="Q43" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="L43" s="3" t="inlineStr"/>
-      <c r="M43" s="3" t="inlineStr"/>
-      <c r="N43" s="3" t="inlineStr"/>
-      <c r="O43" s="5" t="n">
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="P43" s="3" t="inlineStr"/>
-      <c r="Q43" s="3" t="inlineStr"/>
-      <c r="R43" s="3" t="inlineStr"/>
-      <c r="S43" s="3" t="inlineStr"/>
-      <c r="T43" s="3" t="inlineStr">
+      <c r="V43" s="2" t="inlineStr"/>
+      <c r="W43" s="2" t="inlineStr"/>
+      <c r="X43" s="2" t="inlineStr"/>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr">
         <is>
           <t>相信公司</t>
         </is>
       </c>
-      <c r="U43" s="3" t="inlineStr"/>
-      <c r="V43" s="3" t="inlineStr"/>
-      <c r="W43" s="3" t="inlineStr"/>
-      <c r="X43" s="3" t="inlineStr"/>
-      <c r="Y43" s="3" t="inlineStr"/>
-      <c r="Z43" s="3" t="inlineStr"/>
-      <c r="AA43" s="4" t="n">
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr"/>
+      <c r="AE43" s="2" t="inlineStr"/>
+      <c r="AF43" s="2" t="inlineStr"/>
+      <c r="AG43" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="AB43" s="3" t="inlineStr"/>
-      <c r="AC43" s="3" t="inlineStr"/>
-      <c r="AD43" s="3" t="inlineStr"/>
-      <c r="AE43" s="3" t="inlineStr"/>
+      <c r="AH43" s="2" t="inlineStr"/>
+      <c r="AI43" s="2" t="inlineStr"/>
+      <c r="AJ43" s="2" t="inlineStr"/>
+      <c r="AK43" s="2" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>c043</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="3" t="inlineStr">
         <is>
+          <t>dec_takeprofit_01</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
           <t>你的票</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>nidepiao</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>📈</t>
         </is>
       </c>
-      <c r="D44" s="3" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr">
         <is>
           <t>它今天又涨了。卖掉一部分落袋，还是再等等？</t>
         </is>
       </c>
-      <c r="F44" s="3" t="inlineStr">
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>equity&gt;800; equity&gt;cost</t>
         </is>
       </c>
-      <c r="G44" s="3" t="inlineStr"/>
-      <c r="H44" s="3" t="inlineStr">
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M44" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
         <is>
           <t>落袋为安</t>
         </is>
       </c>
-      <c r="I44" s="3" t="inlineStr"/>
-      <c r="J44" s="3" t="inlineStr"/>
-      <c r="K44" s="5" t="n">
+      <c r="O44" s="2" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr"/>
+      <c r="Q44" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="L44" s="3" t="inlineStr"/>
-      <c r="M44" s="3" t="inlineStr"/>
-      <c r="N44" s="3" t="inlineStr"/>
-      <c r="O44" s="5" t="n">
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="P44" s="3" t="inlineStr"/>
-      <c r="Q44" s="3" t="inlineStr"/>
-      <c r="R44" s="3" t="inlineStr"/>
-      <c r="S44" s="3" t="inlineStr"/>
-      <c r="T44" s="3" t="inlineStr">
+      <c r="V44" s="2" t="inlineStr"/>
+      <c r="W44" s="2" t="inlineStr"/>
+      <c r="X44" s="2" t="inlineStr"/>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr">
         <is>
           <t>还能涨，再等等</t>
         </is>
       </c>
-      <c r="U44" s="3" t="inlineStr"/>
-      <c r="V44" s="3" t="inlineStr"/>
-      <c r="W44" s="3" t="inlineStr"/>
-      <c r="X44" s="3" t="inlineStr"/>
-      <c r="Y44" s="3" t="inlineStr"/>
-      <c r="Z44" s="3" t="inlineStr"/>
-      <c r="AA44" s="4" t="n">
+      <c r="AA44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr"/>
+      <c r="AE44" s="2" t="inlineStr"/>
+      <c r="AF44" s="2" t="inlineStr"/>
+      <c r="AG44" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="AB44" s="3" t="inlineStr"/>
-      <c r="AC44" s="3" t="inlineStr"/>
-      <c r="AD44" s="3" t="inlineStr"/>
-      <c r="AE44" s="3" t="inlineStr"/>
+      <c r="AH44" s="2" t="inlineStr"/>
+      <c r="AI44" s="2" t="inlineStr"/>
+      <c r="AJ44" s="2" t="inlineStr"/>
+      <c r="AK44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>c044</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
+          <t>dec_stoploss_01</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
           <t>你的票</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>nidepiao</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>📉</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr">
         <is>
           <t>它已经跌去两成。止损，还是扛着？</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>equity&gt;800; equity&lt;cost*0.85</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr"/>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M45" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
         <is>
           <t>割了</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr"/>
-      <c r="J45" s="3" t="inlineStr"/>
-      <c r="K45" s="5" t="n">
+      <c r="O45" s="2" t="inlineStr"/>
+      <c r="P45" s="2" t="inlineStr"/>
+      <c r="Q45" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L45" s="3" t="inlineStr"/>
-      <c r="M45" s="3" t="inlineStr"/>
-      <c r="N45" s="3" t="inlineStr"/>
-      <c r="O45" s="4" t="n">
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="P45" s="3" t="inlineStr"/>
-      <c r="Q45" s="3" t="inlineStr"/>
-      <c r="R45" s="3" t="inlineStr"/>
-      <c r="S45" s="3" t="inlineStr"/>
-      <c r="T45" s="3" t="inlineStr">
+      <c r="V45" s="2" t="inlineStr"/>
+      <c r="W45" s="2" t="inlineStr"/>
+      <c r="X45" s="2" t="inlineStr"/>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr">
         <is>
           <t>扛着，会回来的</t>
         </is>
       </c>
-      <c r="U45" s="3" t="inlineStr"/>
-      <c r="V45" s="3" t="inlineStr"/>
-      <c r="W45" s="3" t="inlineStr"/>
-      <c r="X45" s="3" t="inlineStr"/>
-      <c r="Y45" s="3" t="inlineStr"/>
-      <c r="Z45" s="3" t="inlineStr"/>
-      <c r="AA45" s="4" t="n">
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr"/>
+      <c r="AE45" s="2" t="inlineStr"/>
+      <c r="AF45" s="2" t="inlineStr"/>
+      <c r="AG45" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="AB45" s="3" t="inlineStr"/>
-      <c r="AC45" s="3" t="inlineStr"/>
-      <c r="AD45" s="3" t="inlineStr"/>
-      <c r="AE45" s="3" t="inlineStr"/>
+      <c r="AH45" s="2" t="inlineStr"/>
+      <c r="AI45" s="2" t="inlineStr"/>
+      <c r="AJ45" s="2" t="inlineStr"/>
+      <c r="AK45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>c045</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="3" t="inlineStr">
         <is>
+          <t>dec_limitup_01</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
           <t>你的票</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>nidepiao</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>🔴</t>
         </is>
       </c>
-      <c r="D46" s="3" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>决策</t>
         </is>
       </c>
-      <c r="E46" s="3" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr">
         <is>
           <t>今天它封住了涨停。群里都在喊明天还有。</t>
         </is>
       </c>
-      <c r="F46" s="3" t="inlineStr">
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>equity&gt;600</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="3" t="inlineStr">
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M46" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
         <is>
           <t>见好就收</t>
         </is>
       </c>
-      <c r="I46" s="3" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr"/>
-      <c r="K46" s="5" t="n">
+      <c r="O46" s="2" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr"/>
+      <c r="Q46" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="L46" s="3" t="inlineStr"/>
-      <c r="M46" s="3" t="inlineStr"/>
-      <c r="N46" s="3" t="inlineStr"/>
-      <c r="O46" s="5" t="n">
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P46" s="3" t="inlineStr"/>
-      <c r="Q46" s="3" t="inlineStr"/>
-      <c r="R46" s="3" t="inlineStr"/>
-      <c r="S46" s="3" t="inlineStr"/>
-      <c r="T46" s="3" t="inlineStr">
+      <c r="V46" s="2" t="inlineStr"/>
+      <c r="W46" s="2" t="inlineStr"/>
+      <c r="X46" s="2" t="inlineStr"/>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr">
         <is>
           <t>拿着，明天还有</t>
         </is>
       </c>
-      <c r="U46" s="3" t="inlineStr"/>
-      <c r="V46" s="3" t="inlineStr"/>
-      <c r="W46" s="3" t="inlineStr"/>
-      <c r="X46" s="3" t="inlineStr"/>
-      <c r="Y46" s="3" t="inlineStr"/>
-      <c r="Z46" s="3" t="inlineStr"/>
-      <c r="AA46" s="4" t="n">
+      <c r="AA46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr"/>
+      <c r="AE46" s="2" t="inlineStr"/>
+      <c r="AF46" s="2" t="inlineStr"/>
+      <c r="AG46" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="AB46" s="3" t="inlineStr"/>
-      <c r="AC46" s="3" t="inlineStr"/>
-      <c r="AD46" s="3" t="inlineStr"/>
-      <c r="AE46" s="3" t="inlineStr"/>
+      <c r="AH46" s="2" t="inlineStr"/>
+      <c r="AI46" s="2" t="inlineStr"/>
+      <c r="AJ46" s="2" t="inlineStr"/>
+      <c r="AK46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>c046</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
+          <t>mkt_bubble_01</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
           <t>所有人</t>
         </is>
       </c>
-      <c r="C47" s="3" t="inlineStr">
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>suoyouren</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>🫧</t>
         </is>
       </c>
-      <c r="D47" s="3" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>市场</t>
         </is>
       </c>
-      <c r="E47" s="3" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr">
         <is>
           <t>半年没人亏过钱了。连门口的保安都在问你买的什么。</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>no:bubble; day&gt;7</t>
         </is>
       </c>
-      <c r="G47" s="3" t="inlineStr">
+      <c r="I47" s="2" t="inlineStr">
         <is>
           <t>bubble:-1</t>
         </is>
       </c>
-      <c r="H47" s="3" t="inlineStr">
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M47" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
         <is>
           <t>我怕了</t>
         </is>
       </c>
-      <c r="I47" s="3" t="inlineStr"/>
-      <c r="J47" s="3" t="inlineStr"/>
-      <c r="K47" s="5" t="n">
+      <c r="O47" s="2" t="inlineStr"/>
+      <c r="P47" s="2" t="inlineStr"/>
+      <c r="Q47" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="L47" s="3" t="inlineStr"/>
-      <c r="M47" s="3" t="inlineStr"/>
-      <c r="N47" s="3" t="inlineStr"/>
-      <c r="O47" s="5" t="n">
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P47" s="3" t="inlineStr"/>
-      <c r="Q47" s="3" t="inlineStr"/>
-      <c r="R47" s="3" t="inlineStr"/>
-      <c r="S47" s="3" t="inlineStr"/>
-      <c r="T47" s="3" t="inlineStr">
+      <c r="V47" s="2" t="inlineStr"/>
+      <c r="W47" s="2" t="inlineStr"/>
+      <c r="X47" s="2" t="inlineStr"/>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr">
         <is>
           <t>我也加点</t>
         </is>
       </c>
-      <c r="U47" s="3" t="inlineStr"/>
-      <c r="V47" s="5" t="n">
+      <c r="AA47" s="2" t="inlineStr"/>
+      <c r="AB47" s="5" t="n">
         <v>4000</v>
       </c>
-      <c r="W47" s="3" t="inlineStr"/>
-      <c r="X47" s="3" t="inlineStr"/>
-      <c r="Y47" s="3" t="inlineStr"/>
-      <c r="Z47" s="3" t="inlineStr"/>
-      <c r="AA47" s="4" t="n">
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr"/>
+      <c r="AE47" s="2" t="inlineStr"/>
+      <c r="AF47" s="2" t="inlineStr"/>
+      <c r="AG47" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="AB47" s="3" t="inlineStr"/>
-      <c r="AC47" s="3" t="inlineStr"/>
-      <c r="AD47" s="3" t="inlineStr"/>
-      <c r="AE47" s="3" t="inlineStr"/>
+      <c r="AH47" s="2" t="inlineStr"/>
+      <c r="AI47" s="2" t="inlineStr"/>
+      <c r="AJ47" s="2" t="inlineStr"/>
+      <c r="AK47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>c047</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="3" t="inlineStr">
         <is>
+          <t>mkt_fomo_01</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
           <t>所有人</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>suoyouren</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>🫧</t>
         </is>
       </c>
-      <c r="D48" s="3" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>市场</t>
         </is>
       </c>
-      <c r="E48" s="3" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr">
         <is>
           <t>菜市场的阿姨开始给你推荐了。她说她也不懂，就是一直在涨。</t>
         </is>
       </c>
-      <c r="F48" s="3" t="inlineStr">
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>has:bubble</t>
         </is>
       </c>
-      <c r="G48" s="3" t="inlineStr"/>
-      <c r="H48" s="3" t="inlineStr">
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M48" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
         <is>
           <t>全部清掉</t>
         </is>
       </c>
-      <c r="I48" s="3" t="inlineStr"/>
-      <c r="J48" s="3" t="inlineStr"/>
-      <c r="K48" s="5" t="n">
+      <c r="O48" s="2" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr"/>
+      <c r="Q48" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L48" s="3" t="inlineStr"/>
-      <c r="M48" s="3" t="inlineStr"/>
-      <c r="N48" s="3" t="inlineStr"/>
-      <c r="O48" s="5" t="n">
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="P48" s="3" t="inlineStr"/>
-      <c r="Q48" s="3" t="inlineStr"/>
-      <c r="R48" s="3" t="inlineStr"/>
-      <c r="S48" s="3" t="inlineStr"/>
-      <c r="T48" s="3" t="inlineStr">
+      <c r="V48" s="2" t="inlineStr"/>
+      <c r="W48" s="2" t="inlineStr"/>
+      <c r="X48" s="2" t="inlineStr"/>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr">
         <is>
           <t>再拿一天</t>
         </is>
       </c>
-      <c r="U48" s="3" t="inlineStr"/>
-      <c r="V48" s="3" t="inlineStr"/>
-      <c r="W48" s="3" t="inlineStr"/>
-      <c r="X48" s="3" t="inlineStr"/>
-      <c r="Y48" s="3" t="inlineStr"/>
-      <c r="Z48" s="3" t="inlineStr"/>
-      <c r="AA48" s="4" t="n">
+      <c r="AA48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr"/>
+      <c r="AE48" s="2" t="inlineStr"/>
+      <c r="AF48" s="2" t="inlineStr"/>
+      <c r="AG48" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="AB48" s="3" t="inlineStr"/>
-      <c r="AC48" s="3" t="inlineStr"/>
-      <c r="AD48" s="3" t="inlineStr"/>
-      <c r="AE48" s="3" t="inlineStr"/>
+      <c r="AH48" s="2" t="inlineStr"/>
+      <c r="AI48" s="2" t="inlineStr"/>
+      <c r="AJ48" s="2" t="inlineStr"/>
+      <c r="AK48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>c048</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="3" t="inlineStr">
         <is>
+          <t>mkt_paperwin_01</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
           <t>你的票</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>nidepiao</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>🤩</t>
         </is>
       </c>
-      <c r="D49" s="3" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>市场</t>
         </is>
       </c>
-      <c r="E49" s="3" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr">
         <is>
           <t>你赚的钱，已经比一整年工资还多。</t>
         </is>
       </c>
-      <c r="F49" s="3" t="inlineStr">
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>has:bubble; equity&gt;1000</t>
         </is>
       </c>
-      <c r="G49" s="3" t="inlineStr"/>
-      <c r="H49" s="3" t="inlineStr">
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M49" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
         <is>
           <t>够了，走人</t>
         </is>
       </c>
-      <c r="I49" s="3" t="inlineStr"/>
-      <c r="J49" s="3" t="inlineStr"/>
-      <c r="K49" s="5" t="n">
+      <c r="O49" s="2" t="inlineStr"/>
+      <c r="P49" s="2" t="inlineStr"/>
+      <c r="Q49" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L49" s="3" t="inlineStr"/>
-      <c r="M49" s="3" t="inlineStr"/>
-      <c r="N49" s="3" t="inlineStr"/>
-      <c r="O49" s="5" t="n">
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="P49" s="3" t="inlineStr"/>
-      <c r="Q49" s="3" t="inlineStr"/>
-      <c r="R49" s="3" t="inlineStr"/>
-      <c r="S49" s="3" t="inlineStr"/>
-      <c r="T49" s="3" t="inlineStr">
+      <c r="V49" s="2" t="inlineStr"/>
+      <c r="W49" s="2" t="inlineStr"/>
+      <c r="X49" s="2" t="inlineStr"/>
+      <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr">
         <is>
           <t>还能更多</t>
         </is>
       </c>
-      <c r="U49" s="3" t="inlineStr"/>
-      <c r="V49" s="3" t="inlineStr"/>
-      <c r="W49" s="3" t="inlineStr"/>
-      <c r="X49" s="3" t="inlineStr"/>
-      <c r="Y49" s="3" t="inlineStr"/>
-      <c r="Z49" s="3" t="inlineStr"/>
-      <c r="AA49" s="4" t="n">
+      <c r="AA49" s="2" t="inlineStr"/>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr"/>
+      <c r="AE49" s="2" t="inlineStr"/>
+      <c r="AF49" s="2" t="inlineStr"/>
+      <c r="AG49" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="AB49" s="3" t="inlineStr"/>
-      <c r="AC49" s="3" t="inlineStr"/>
-      <c r="AD49" s="3" t="inlineStr"/>
-      <c r="AE49" s="3" t="inlineStr"/>
+      <c r="AH49" s="2" t="inlineStr"/>
+      <c r="AI49" s="2" t="inlineStr"/>
+      <c r="AJ49" s="2" t="inlineStr"/>
+      <c r="AK49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>c049</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="3" t="inlineStr">
         <is>
+          <t>mkt_crisis_01</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
           <t>新闻头条</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>xinwentoutiao</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>❄️</t>
         </is>
       </c>
-      <c r="D50" s="3" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>市场</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>有一家很大的银行，一夜之间没了。街上没人笑得出来。</t>
         </is>
       </c>
-      <c r="F50" s="3" t="inlineStr">
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>no:crisis; day&gt;11</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="I50" s="2" t="inlineStr">
         <is>
           <t>crisis:12</t>
         </is>
       </c>
-      <c r="H50" s="3" t="inlineStr">
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M50" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
         <is>
           <t>先躲一躲</t>
         </is>
       </c>
-      <c r="I50" s="3" t="inlineStr"/>
-      <c r="J50" s="3" t="inlineStr"/>
-      <c r="K50" s="5" t="n">
+      <c r="O50" s="2" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr"/>
+      <c r="Q50" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="L50" s="3" t="inlineStr"/>
-      <c r="M50" s="3" t="inlineStr"/>
-      <c r="N50" s="3" t="inlineStr"/>
-      <c r="O50" s="5" t="n">
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P50" s="3" t="inlineStr"/>
-      <c r="Q50" s="3" t="inlineStr"/>
-      <c r="R50" s="3" t="inlineStr"/>
-      <c r="S50" s="3" t="inlineStr"/>
-      <c r="T50" s="3" t="inlineStr">
+      <c r="V50" s="2" t="inlineStr"/>
+      <c r="W50" s="2" t="inlineStr"/>
+      <c r="X50" s="2" t="inlineStr"/>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr">
         <is>
           <t>这是抄底的机会</t>
         </is>
       </c>
-      <c r="U50" s="3" t="inlineStr"/>
-      <c r="V50" s="5" t="n">
+      <c r="AA50" s="2" t="inlineStr"/>
+      <c r="AB50" s="5" t="n">
         <v>2500</v>
       </c>
-      <c r="W50" s="3" t="inlineStr"/>
-      <c r="X50" s="3" t="inlineStr"/>
-      <c r="Y50" s="3" t="inlineStr"/>
-      <c r="Z50" s="3" t="inlineStr"/>
-      <c r="AA50" s="4" t="n">
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr"/>
+      <c r="AE50" s="2" t="inlineStr"/>
+      <c r="AF50" s="2" t="inlineStr"/>
+      <c r="AG50" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="AB50" s="3" t="inlineStr"/>
-      <c r="AC50" s="3" t="inlineStr"/>
-      <c r="AD50" s="3" t="inlineStr"/>
-      <c r="AE50" s="3" t="inlineStr"/>
+      <c r="AH50" s="2" t="inlineStr"/>
+      <c r="AI50" s="2" t="inlineStr"/>
+      <c r="AJ50" s="2" t="inlineStr"/>
+      <c r="AK50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>c050</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="3" t="inlineStr">
         <is>
+          <t>mkt_panic_01</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
           <t>公司群</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>gongsiqun</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>❄️</t>
         </is>
       </c>
-      <c r="D51" s="3" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>市场</t>
         </is>
       </c>
-      <c r="E51" s="3" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>群里在传第三轮裁员。这次是真的。</t>
         </is>
       </c>
-      <c r="F51" s="3" t="inlineStr">
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>has:crisis</t>
         </is>
       </c>
-      <c r="G51" s="3" t="inlineStr"/>
-      <c r="H51" s="3" t="inlineStr">
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M51" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
         <is>
           <t>认了，先跑</t>
         </is>
       </c>
-      <c r="I51" s="3" t="inlineStr"/>
-      <c r="J51" s="3" t="inlineStr"/>
-      <c r="K51" s="5" t="n">
+      <c r="O51" s="2" t="inlineStr"/>
+      <c r="P51" s="2" t="inlineStr"/>
+      <c r="Q51" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="L51" s="3" t="inlineStr"/>
-      <c r="M51" s="3" t="inlineStr"/>
-      <c r="N51" s="3" t="inlineStr"/>
-      <c r="O51" s="4" t="n">
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="P51" s="3" t="inlineStr"/>
-      <c r="Q51" s="3" t="inlineStr"/>
-      <c r="R51" s="3" t="inlineStr"/>
-      <c r="S51" s="3" t="inlineStr"/>
-      <c r="T51" s="3" t="inlineStr">
+      <c r="V51" s="2" t="inlineStr"/>
+      <c r="W51" s="2" t="inlineStr"/>
+      <c r="X51" s="2" t="inlineStr"/>
+      <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr">
         <is>
           <t>再扛一天</t>
         </is>
       </c>
-      <c r="U51" s="3" t="inlineStr"/>
-      <c r="V51" s="3" t="inlineStr"/>
-      <c r="W51" s="3" t="inlineStr"/>
-      <c r="X51" s="3" t="inlineStr"/>
-      <c r="Y51" s="3" t="inlineStr"/>
-      <c r="Z51" s="3" t="inlineStr"/>
-      <c r="AA51" s="4" t="n">
+      <c r="AA51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr"/>
+      <c r="AE51" s="2" t="inlineStr"/>
+      <c r="AF51" s="2" t="inlineStr"/>
+      <c r="AG51" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB51" s="3" t="inlineStr"/>
-      <c r="AC51" s="3" t="inlineStr"/>
-      <c r="AD51" s="3" t="inlineStr"/>
-      <c r="AE51" s="3" t="inlineStr"/>
+      <c r="AH51" s="2" t="inlineStr"/>
+      <c r="AI51" s="2" t="inlineStr"/>
+      <c r="AJ51" s="2" t="inlineStr"/>
+      <c r="AK51" s="2" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>c051</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="3" t="inlineStr">
         <is>
+          <t>mkt_halt_01</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
           <t>交易所</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>jiaoyisuo</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>🚫</t>
         </is>
       </c>
-      <c r="D52" s="3" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>市场</t>
         </is>
       </c>
-      <c r="E52" s="3" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>公司公告：筹划重大事项，明日起停牌，复牌时间待定。</t>
         </is>
       </c>
-      <c r="F52" s="3" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>no:halt; equity&gt;500</t>
         </is>
       </c>
-      <c r="G52" s="3" t="inlineStr">
+      <c r="I52" s="2" t="inlineStr">
         <is>
           <t>halt:5</t>
         </is>
       </c>
-      <c r="H52" s="3" t="inlineStr">
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M52" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N52" s="2" t="inlineStr">
         <is>
           <t>拿着等消息</t>
         </is>
       </c>
-      <c r="I52" s="3" t="inlineStr"/>
-      <c r="J52" s="3" t="inlineStr"/>
-      <c r="K52" s="3" t="inlineStr"/>
-      <c r="L52" s="3" t="inlineStr"/>
-      <c r="M52" s="3" t="inlineStr"/>
-      <c r="N52" s="3" t="inlineStr"/>
-      <c r="O52" s="4" t="n">
+      <c r="O52" s="2" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr"/>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="P52" s="3" t="inlineStr"/>
-      <c r="Q52" s="3" t="inlineStr"/>
-      <c r="R52" s="3" t="inlineStr"/>
-      <c r="S52" s="3" t="inlineStr"/>
-      <c r="T52" s="3" t="inlineStr">
+      <c r="V52" s="2" t="inlineStr"/>
+      <c r="W52" s="2" t="inlineStr"/>
+      <c r="X52" s="2" t="inlineStr"/>
+      <c r="Y52" s="2" t="inlineStr"/>
+      <c r="Z52" s="2" t="inlineStr">
         <is>
           <t>赶紧先卖出来</t>
         </is>
       </c>
-      <c r="U52" s="3" t="inlineStr"/>
-      <c r="V52" s="3" t="inlineStr"/>
-      <c r="W52" s="5" t="n">
+      <c r="AA52" s="2" t="inlineStr"/>
+      <c r="AB52" s="2" t="inlineStr"/>
+      <c r="AC52" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="X52" s="3" t="inlineStr"/>
-      <c r="Y52" s="3" t="inlineStr"/>
-      <c r="Z52" s="3" t="inlineStr"/>
-      <c r="AA52" s="4" t="n">
+      <c r="AD52" s="2" t="inlineStr"/>
+      <c r="AE52" s="2" t="inlineStr"/>
+      <c r="AF52" s="2" t="inlineStr"/>
+      <c r="AG52" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="AB52" s="3" t="inlineStr"/>
-      <c r="AC52" s="3" t="inlineStr"/>
-      <c r="AD52" s="3" t="inlineStr"/>
-      <c r="AE52" s="3" t="inlineStr"/>
+      <c r="AH52" s="2" t="inlineStr"/>
+      <c r="AI52" s="2" t="inlineStr"/>
+      <c r="AJ52" s="2" t="inlineStr"/>
+      <c r="AK52" s="2" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>c052</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="3" t="inlineStr">
         <is>
+          <t>mkt_haltwait_01</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
           <t>交易所</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>jiaoyisuo</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>🚫</t>
         </is>
       </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>市场</t>
         </is>
       </c>
-      <c r="E53" s="3" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr">
         <is>
           <t>还是没有复牌的消息。</t>
         </is>
       </c>
-      <c r="F53" s="3" t="inlineStr">
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>has:halt</t>
         </is>
       </c>
-      <c r="G53" s="3" t="inlineStr"/>
-      <c r="H53" s="3" t="inlineStr">
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M53" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
         <is>
           <t>不看就不难受</t>
         </is>
       </c>
-      <c r="I53" s="3" t="inlineStr"/>
-      <c r="J53" s="3" t="inlineStr"/>
-      <c r="K53" s="3" t="inlineStr"/>
-      <c r="L53" s="3" t="inlineStr"/>
-      <c r="M53" s="3" t="inlineStr"/>
-      <c r="N53" s="3" t="inlineStr"/>
-      <c r="O53" s="5" t="n">
+      <c r="O53" s="2" t="inlineStr"/>
+      <c r="P53" s="2" t="inlineStr"/>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="P53" s="3" t="inlineStr"/>
-      <c r="Q53" s="3" t="inlineStr"/>
-      <c r="R53" s="3" t="inlineStr"/>
-      <c r="S53" s="3" t="inlineStr"/>
-      <c r="T53" s="3" t="inlineStr">
+      <c r="V53" s="2" t="inlineStr"/>
+      <c r="W53" s="2" t="inlineStr"/>
+      <c r="X53" s="2" t="inlineStr"/>
+      <c r="Y53" s="2" t="inlineStr"/>
+      <c r="Z53" s="2" t="inlineStr">
         <is>
           <t>刷公告</t>
         </is>
       </c>
-      <c r="U53" s="3" t="inlineStr"/>
-      <c r="V53" s="3" t="inlineStr"/>
-      <c r="W53" s="3" t="inlineStr"/>
-      <c r="X53" s="3" t="inlineStr"/>
-      <c r="Y53" s="3" t="inlineStr"/>
-      <c r="Z53" s="3" t="inlineStr"/>
-      <c r="AA53" s="4" t="n">
+      <c r="AA53" s="2" t="inlineStr"/>
+      <c r="AB53" s="2" t="inlineStr"/>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr"/>
+      <c r="AE53" s="2" t="inlineStr"/>
+      <c r="AF53" s="2" t="inlineStr"/>
+      <c r="AG53" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="AB53" s="3" t="inlineStr"/>
-      <c r="AC53" s="3" t="inlineStr"/>
-      <c r="AD53" s="3" t="inlineStr"/>
-      <c r="AE53" s="3" t="inlineStr"/>
+      <c r="AH53" s="2" t="inlineStr"/>
+      <c r="AI53" s="2" t="inlineStr"/>
+      <c r="AJ53" s="2" t="inlineStr"/>
+      <c r="AK53" s="2" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>c053</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="3" t="inlineStr">
         <is>
+          <t>risk_margin_01</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
           <t>配资公司</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>peizigongsi</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>📞</t>
         </is>
       </c>
-      <c r="D54" s="3" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>风险</t>
         </is>
       </c>
-      <c r="E54" s="3" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>您好，十倍杠杆，资金秒到账，日息只要万分之八。</t>
         </is>
       </c>
-      <c r="F54" s="3" t="inlineStr"/>
-      <c r="G54" s="3" t="inlineStr"/>
-      <c r="H54" s="3" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr"/>
+      <c r="I54" s="2" t="inlineStr"/>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M54" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
         <is>
           <t>直接挂断</t>
         </is>
       </c>
-      <c r="I54" s="3" t="inlineStr"/>
-      <c r="J54" s="3" t="inlineStr"/>
-      <c r="K54" s="3" t="inlineStr"/>
-      <c r="L54" s="3" t="inlineStr"/>
-      <c r="M54" s="3" t="inlineStr"/>
-      <c r="N54" s="3" t="inlineStr"/>
-      <c r="O54" s="5" t="n">
+      <c r="O54" s="2" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr"/>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P54" s="3" t="inlineStr"/>
-      <c r="Q54" s="3" t="inlineStr"/>
-      <c r="R54" s="3" t="inlineStr"/>
-      <c r="S54" s="3" t="inlineStr"/>
-      <c r="T54" s="3" t="inlineStr">
+      <c r="V54" s="2" t="inlineStr"/>
+      <c r="W54" s="2" t="inlineStr"/>
+      <c r="X54" s="2" t="inlineStr"/>
+      <c r="Y54" s="2" t="inlineStr"/>
+      <c r="Z54" s="2" t="inlineStr">
         <is>
           <t>先配 12,000</t>
         </is>
       </c>
-      <c r="U54" s="3" t="inlineStr"/>
-      <c r="V54" s="3" t="inlineStr"/>
-      <c r="W54" s="3" t="inlineStr"/>
-      <c r="X54" s="5" t="n">
+      <c r="AA54" s="2" t="inlineStr"/>
+      <c r="AB54" s="2" t="inlineStr"/>
+      <c r="AC54" s="2" t="inlineStr"/>
+      <c r="AD54" s="5" t="n">
         <v>12000</v>
       </c>
-      <c r="Y54" s="3" t="inlineStr"/>
-      <c r="Z54" s="3" t="inlineStr"/>
-      <c r="AA54" s="4" t="n">
+      <c r="AE54" s="2" t="inlineStr"/>
+      <c r="AF54" s="2" t="inlineStr"/>
+      <c r="AG54" s="4" t="n">
         <v>-8</v>
       </c>
-      <c r="AB54" s="3" t="inlineStr"/>
-      <c r="AC54" s="3" t="inlineStr"/>
-      <c r="AD54" s="3" t="inlineStr"/>
-      <c r="AE54" s="3" t="inlineStr"/>
+      <c r="AH54" s="2" t="inlineStr"/>
+      <c r="AI54" s="2" t="inlineStr"/>
+      <c r="AJ54" s="2" t="inlineStr"/>
+      <c r="AK54" s="2" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>c054</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="3" t="inlineStr">
         <is>
+          <t>risk_loanad_01</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
           <t>网贷广告</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>wangdai</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>📱</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>风险</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>额度 50,000，日息万三，三分钟到账。</t>
         </is>
       </c>
-      <c r="F55" s="3" t="inlineStr"/>
-      <c r="G55" s="3" t="inlineStr"/>
-      <c r="H55" s="3" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr"/>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M55" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N55" s="2" t="inlineStr">
         <is>
           <t>关掉</t>
         </is>
       </c>
-      <c r="I55" s="3" t="inlineStr"/>
-      <c r="J55" s="3" t="inlineStr"/>
-      <c r="K55" s="3" t="inlineStr"/>
-      <c r="L55" s="3" t="inlineStr"/>
-      <c r="M55" s="3" t="inlineStr"/>
-      <c r="N55" s="3" t="inlineStr"/>
-      <c r="O55" s="5" t="n">
+      <c r="O55" s="2" t="inlineStr"/>
+      <c r="P55" s="2" t="inlineStr"/>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="P55" s="3" t="inlineStr"/>
-      <c r="Q55" s="3" t="inlineStr"/>
-      <c r="R55" s="3" t="inlineStr"/>
-      <c r="S55" s="3" t="inlineStr"/>
-      <c r="T55" s="3" t="inlineStr">
+      <c r="V55" s="2" t="inlineStr"/>
+      <c r="W55" s="2" t="inlineStr"/>
+      <c r="X55" s="2" t="inlineStr"/>
+      <c r="Y55" s="2" t="inlineStr"/>
+      <c r="Z55" s="2" t="inlineStr">
         <is>
           <t>借来抄底</t>
         </is>
       </c>
-      <c r="U55" s="3" t="inlineStr"/>
-      <c r="V55" s="3" t="inlineStr"/>
-      <c r="W55" s="3" t="inlineStr"/>
-      <c r="X55" s="5" t="n">
+      <c r="AA55" s="2" t="inlineStr"/>
+      <c r="AB55" s="2" t="inlineStr"/>
+      <c r="AC55" s="2" t="inlineStr"/>
+      <c r="AD55" s="5" t="n">
         <v>12000</v>
       </c>
-      <c r="Y55" s="3" t="inlineStr"/>
-      <c r="Z55" s="3" t="inlineStr"/>
-      <c r="AA55" s="4" t="n">
+      <c r="AE55" s="2" t="inlineStr"/>
+      <c r="AF55" s="2" t="inlineStr"/>
+      <c r="AG55" s="4" t="n">
         <v>-9</v>
       </c>
-      <c r="AB55" s="3" t="inlineStr"/>
-      <c r="AC55" s="3" t="inlineStr"/>
-      <c r="AD55" s="3" t="inlineStr"/>
-      <c r="AE55" s="3" t="inlineStr"/>
+      <c r="AH55" s="2" t="inlineStr"/>
+      <c r="AI55" s="2" t="inlineStr"/>
+      <c r="AJ55" s="2" t="inlineStr"/>
+      <c r="AK55" s="2" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>c055</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="3" t="inlineStr">
         <is>
+          <t>risk_card_01</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
           <t>信用卡</t>
         </is>
       </c>
-      <c r="C56" s="3" t="inlineStr">
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>xinyongka</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>💳</t>
         </is>
       </c>
-      <c r="D56" s="3" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>风险</t>
         </is>
       </c>
-      <c r="E56" s="3" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr">
         <is>
           <t>账单 8,000。还最低，还是还全额？</t>
         </is>
       </c>
-      <c r="F56" s="3" t="inlineStr"/>
-      <c r="G56" s="3" t="inlineStr"/>
-      <c r="H56" s="3" t="inlineStr">
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M56" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
         <is>
           <t>咬牙全额还</t>
         </is>
       </c>
-      <c r="I56" s="5" t="n">
+      <c r="O56" s="5" t="n">
         <v>10400</v>
       </c>
-      <c r="J56" s="3" t="inlineStr"/>
-      <c r="K56" s="3" t="inlineStr"/>
-      <c r="L56" s="3" t="inlineStr"/>
-      <c r="M56" s="3" t="inlineStr"/>
-      <c r="N56" s="3" t="inlineStr"/>
-      <c r="O56" s="5" t="n">
+      <c r="P56" s="2" t="inlineStr"/>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P56" s="3" t="inlineStr"/>
-      <c r="Q56" s="3" t="inlineStr"/>
-      <c r="R56" s="3" t="inlineStr"/>
-      <c r="S56" s="3" t="inlineStr"/>
-      <c r="T56" s="3" t="inlineStr">
+      <c r="V56" s="2" t="inlineStr"/>
+      <c r="W56" s="2" t="inlineStr"/>
+      <c r="X56" s="2" t="inlineStr"/>
+      <c r="Y56" s="2" t="inlineStr"/>
+      <c r="Z56" s="2" t="inlineStr">
         <is>
           <t>还最低</t>
         </is>
       </c>
-      <c r="U56" s="3" t="inlineStr"/>
-      <c r="V56" s="3" t="inlineStr"/>
-      <c r="W56" s="3" t="inlineStr"/>
-      <c r="X56" s="5" t="n">
+      <c r="AA56" s="2" t="inlineStr"/>
+      <c r="AB56" s="2" t="inlineStr"/>
+      <c r="AC56" s="2" t="inlineStr"/>
+      <c r="AD56" s="5" t="n">
         <v>8000</v>
       </c>
-      <c r="Y56" s="3" t="inlineStr"/>
-      <c r="Z56" s="3" t="inlineStr"/>
-      <c r="AA56" s="4" t="n">
+      <c r="AE56" s="2" t="inlineStr"/>
+      <c r="AF56" s="2" t="inlineStr"/>
+      <c r="AG56" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="AB56" s="3" t="inlineStr"/>
-      <c r="AC56" s="3" t="inlineStr"/>
-      <c r="AD56" s="3" t="inlineStr"/>
-      <c r="AE56" s="3" t="inlineStr"/>
+      <c r="AH56" s="2" t="inlineStr"/>
+      <c r="AI56" s="2" t="inlineStr"/>
+      <c r="AJ56" s="2" t="inlineStr"/>
+      <c r="AK56" s="2" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>c056</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="3" t="inlineStr">
         <is>
+          <t>risk_scam_01</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
           <t>荐股群</t>
         </is>
       </c>
-      <c r="C57" s="3" t="inlineStr">
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>jianguqun</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>🎯</t>
         </is>
       </c>
-      <c r="D57" s="3" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>风险</t>
         </is>
       </c>
-      <c r="E57" s="3" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr">
         <is>
           <t>老师说跟着操作一年十倍，先交 8,888 会员费，名额有限。</t>
         </is>
       </c>
-      <c r="F57" s="3" t="inlineStr"/>
-      <c r="G57" s="3" t="inlineStr"/>
-      <c r="H57" s="3" t="inlineStr">
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="2" t="inlineStr"/>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M57" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
         <is>
           <t>这就是骗局</t>
         </is>
       </c>
-      <c r="I57" s="3" t="inlineStr"/>
-      <c r="J57" s="3" t="inlineStr"/>
-      <c r="K57" s="3" t="inlineStr"/>
-      <c r="L57" s="3" t="inlineStr"/>
-      <c r="M57" s="3" t="inlineStr"/>
-      <c r="N57" s="3" t="inlineStr"/>
-      <c r="O57" s="5" t="n">
+      <c r="O57" s="2" t="inlineStr"/>
+      <c r="P57" s="2" t="inlineStr"/>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="P57" s="3" t="inlineStr"/>
-      <c r="Q57" s="3" t="inlineStr"/>
-      <c r="R57" s="3" t="inlineStr"/>
-      <c r="S57" s="3" t="inlineStr"/>
-      <c r="T57" s="3" t="inlineStr">
+      <c r="V57" s="2" t="inlineStr"/>
+      <c r="W57" s="2" t="inlineStr"/>
+      <c r="X57" s="2" t="inlineStr"/>
+      <c r="Y57" s="2" t="inlineStr"/>
+      <c r="Z57" s="2" t="inlineStr">
         <is>
           <t>交钱</t>
         </is>
       </c>
-      <c r="U57" s="5" t="n">
+      <c r="AA57" s="5" t="n">
         <v>3900</v>
       </c>
-      <c r="V57" s="3" t="inlineStr"/>
-      <c r="W57" s="3" t="inlineStr"/>
-      <c r="X57" s="3" t="inlineStr"/>
-      <c r="Y57" s="3" t="inlineStr"/>
-      <c r="Z57" s="3" t="inlineStr"/>
-      <c r="AA57" s="4" t="n">
+      <c r="AB57" s="2" t="inlineStr"/>
+      <c r="AC57" s="2" t="inlineStr"/>
+      <c r="AD57" s="2" t="inlineStr"/>
+      <c r="AE57" s="2" t="inlineStr"/>
+      <c r="AF57" s="2" t="inlineStr"/>
+      <c r="AG57" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="AB57" s="5" t="n">
+      <c r="AH57" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="AC57" s="3" t="inlineStr"/>
-      <c r="AD57" s="3" t="inlineStr"/>
-      <c r="AE57" s="3" t="inlineStr"/>
+      <c r="AI57" s="2" t="inlineStr"/>
+      <c r="AJ57" s="2" t="inlineStr"/>
+      <c r="AK57" s="2" t="inlineStr"/>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>c057</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="3" t="inlineStr">
         <is>
+          <t>risk_influencer_01</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
           <t>大 V</t>
         </is>
       </c>
-      <c r="C58" s="3" t="inlineStr">
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>dawei</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>⭐</t>
         </is>
       </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>风险</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr">
         <is>
           <t>十万粉丝的大 V 深夜发文：这是十年一遇的机会，闭眼买。</t>
         </is>
       </c>
-      <c r="F58" s="3" t="inlineStr"/>
-      <c r="G58" s="3" t="inlineStr"/>
-      <c r="H58" s="3" t="inlineStr">
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="2" t="inlineStr"/>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M58" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
         <is>
           <t>大 V 也亏钱</t>
         </is>
       </c>
-      <c r="I58" s="3" t="inlineStr"/>
-      <c r="J58" s="3" t="inlineStr"/>
-      <c r="K58" s="3" t="inlineStr"/>
-      <c r="L58" s="3" t="inlineStr"/>
-      <c r="M58" s="3" t="inlineStr"/>
-      <c r="N58" s="3" t="inlineStr"/>
-      <c r="O58" s="5" t="n">
+      <c r="O58" s="2" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr"/>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="P58" s="3" t="inlineStr"/>
-      <c r="Q58" s="3" t="inlineStr"/>
-      <c r="R58" s="3" t="inlineStr"/>
-      <c r="S58" s="3" t="inlineStr"/>
-      <c r="T58" s="3" t="inlineStr">
+      <c r="V58" s="2" t="inlineStr"/>
+      <c r="W58" s="2" t="inlineStr"/>
+      <c r="X58" s="2" t="inlineStr"/>
+      <c r="Y58" s="2" t="inlineStr"/>
+      <c r="Z58" s="2" t="inlineStr">
         <is>
           <t>跟 3,000</t>
         </is>
       </c>
-      <c r="U58" s="3" t="inlineStr"/>
-      <c r="V58" s="5" t="n">
+      <c r="AA58" s="2" t="inlineStr"/>
+      <c r="AB58" s="5" t="n">
         <v>3000</v>
       </c>
-      <c r="W58" s="3" t="inlineStr"/>
-      <c r="X58" s="3" t="inlineStr"/>
-      <c r="Y58" s="3" t="inlineStr"/>
-      <c r="Z58" s="3" t="inlineStr"/>
-      <c r="AA58" s="4" t="n">
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr"/>
+      <c r="AE58" s="2" t="inlineStr"/>
+      <c r="AF58" s="2" t="inlineStr"/>
+      <c r="AG58" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="AB58" s="5" t="n">
+      <c r="AH58" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="AC58" s="3" t="inlineStr"/>
-      <c r="AD58" s="3" t="inlineStr"/>
-      <c r="AE58" s="3" t="inlineStr"/>
+      <c r="AI58" s="2" t="inlineStr"/>
+      <c r="AJ58" s="2" t="inlineStr"/>
+      <c r="AK58" s="2" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>c058</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="3" t="inlineStr">
         <is>
+          <t>risk_leak_01</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
           <t>微信群</t>
         </is>
       </c>
-      <c r="C59" s="3" t="inlineStr">
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>weixinqun</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>👥</t>
         </is>
       </c>
-      <c r="D59" s="3" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>风险</t>
         </is>
       </c>
-      <c r="E59" s="3" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>群里有人说，这只票下周要有大动作，内部消息。</t>
         </is>
       </c>
-      <c r="F59" s="3" t="inlineStr"/>
-      <c r="G59" s="3" t="inlineStr"/>
-      <c r="H59" s="3" t="inlineStr">
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M59" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
         <is>
           <t>这话我听过二十遍</t>
         </is>
       </c>
-      <c r="I59" s="3" t="inlineStr"/>
-      <c r="J59" s="3" t="inlineStr"/>
-      <c r="K59" s="3" t="inlineStr"/>
-      <c r="L59" s="3" t="inlineStr"/>
-      <c r="M59" s="3" t="inlineStr"/>
-      <c r="N59" s="3" t="inlineStr"/>
-      <c r="O59" s="5" t="n">
+      <c r="O59" s="2" t="inlineStr"/>
+      <c r="P59" s="2" t="inlineStr"/>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="P59" s="3" t="inlineStr"/>
-      <c r="Q59" s="3" t="inlineStr"/>
-      <c r="R59" s="3" t="inlineStr"/>
-      <c r="S59" s="3" t="inlineStr"/>
-      <c r="T59" s="3" t="inlineStr">
+      <c r="V59" s="2" t="inlineStr"/>
+      <c r="W59" s="2" t="inlineStr"/>
+      <c r="X59" s="2" t="inlineStr"/>
+      <c r="Y59" s="2" t="inlineStr"/>
+      <c r="Z59" s="2" t="inlineStr">
         <is>
           <t>满仓埋伏</t>
         </is>
       </c>
-      <c r="U59" s="3" t="inlineStr"/>
-      <c r="V59" s="5" t="n">
+      <c r="AA59" s="2" t="inlineStr"/>
+      <c r="AB59" s="5" t="n">
         <v>4000</v>
       </c>
-      <c r="W59" s="3" t="inlineStr"/>
-      <c r="X59" s="3" t="inlineStr"/>
-      <c r="Y59" s="3" t="inlineStr"/>
-      <c r="Z59" s="3" t="inlineStr"/>
-      <c r="AA59" s="4" t="n">
+      <c r="AC59" s="2" t="inlineStr"/>
+      <c r="AD59" s="2" t="inlineStr"/>
+      <c r="AE59" s="2" t="inlineStr"/>
+      <c r="AF59" s="2" t="inlineStr"/>
+      <c r="AG59" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB59" s="5" t="n">
+      <c r="AH59" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="AC59" s="3" t="inlineStr"/>
-      <c r="AD59" s="3" t="inlineStr"/>
-      <c r="AE59" s="3" t="inlineStr"/>
+      <c r="AI59" s="2" t="inlineStr"/>
+      <c r="AJ59" s="2" t="inlineStr"/>
+      <c r="AK59" s="2" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>c059</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="3" t="inlineStr">
         <is>
+          <t>risk_callmargin_01</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
           <t>券商短信</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>quanshang</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>📲</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>风险</t>
         </is>
       </c>
-      <c r="E60" s="3" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr">
         <is>
           <t>你借的钱快不够抵押了，请追加保证金。</t>
         </is>
       </c>
-      <c r="F60" s="3" t="inlineStr">
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>risk&gt;34 | debt&gt;8000</t>
         </is>
       </c>
-      <c r="G60" s="3" t="inlineStr"/>
-      <c r="H60" s="3" t="inlineStr">
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M60" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
         <is>
           <t>认了，让他们卖</t>
         </is>
       </c>
-      <c r="I60" s="3" t="inlineStr"/>
-      <c r="J60" s="3" t="inlineStr"/>
-      <c r="K60" s="5" t="n">
+      <c r="O60" s="2" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr"/>
+      <c r="Q60" s="5" t="n">
         <v>0.6</v>
       </c>
-      <c r="L60" s="3" t="inlineStr"/>
-      <c r="M60" s="3" t="inlineStr"/>
-      <c r="N60" s="3" t="inlineStr"/>
-      <c r="O60" s="4" t="n">
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="4" t="n">
         <v>-8</v>
       </c>
-      <c r="P60" s="4" t="n">
+      <c r="V60" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="Q60" s="3" t="inlineStr"/>
-      <c r="R60" s="3" t="inlineStr"/>
-      <c r="S60" s="3" t="inlineStr"/>
-      <c r="T60" s="3" t="inlineStr">
+      <c r="W60" s="2" t="inlineStr"/>
+      <c r="X60" s="2" t="inlineStr"/>
+      <c r="Y60" s="2" t="inlineStr"/>
+      <c r="Z60" s="2" t="inlineStr">
         <is>
           <t>再借 5,000 补上</t>
         </is>
       </c>
-      <c r="U60" s="3" t="inlineStr"/>
-      <c r="V60" s="3" t="inlineStr"/>
-      <c r="W60" s="3" t="inlineStr"/>
-      <c r="X60" s="5" t="n">
+      <c r="AA60" s="2" t="inlineStr"/>
+      <c r="AB60" s="2" t="inlineStr"/>
+      <c r="AC60" s="2" t="inlineStr"/>
+      <c r="AD60" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="Y60" s="3" t="inlineStr"/>
-      <c r="Z60" s="3" t="inlineStr"/>
-      <c r="AA60" s="4" t="n">
+      <c r="AE60" s="2" t="inlineStr"/>
+      <c r="AF60" s="2" t="inlineStr"/>
+      <c r="AG60" s="4" t="n">
         <v>-6</v>
       </c>
-      <c r="AB60" s="3" t="inlineStr"/>
-      <c r="AC60" s="3" t="inlineStr"/>
-      <c r="AD60" s="3" t="inlineStr"/>
-      <c r="AE60" s="3" t="inlineStr"/>
+      <c r="AH60" s="2" t="inlineStr"/>
+      <c r="AI60" s="2" t="inlineStr"/>
+      <c r="AJ60" s="2" t="inlineStr"/>
+      <c r="AK60" s="2" t="inlineStr"/>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>c060</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="3" t="inlineStr">
         <is>
+          <t>risk_repay_01</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
           <t>你的债</t>
         </is>
       </c>
-      <c r="C61" s="3" t="inlineStr">
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>nidezhai</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>🧮</t>
         </is>
       </c>
-      <c r="D61" s="3" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>风险</t>
         </is>
       </c>
-      <c r="E61" s="3" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr">
         <is>
           <t>要不要先把欠的钱还掉一部分？</t>
         </is>
       </c>
-      <c r="F61" s="3" t="inlineStr">
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>debt&gt;3000</t>
         </is>
       </c>
-      <c r="G61" s="3" t="inlineStr"/>
-      <c r="H61" s="3" t="inlineStr">
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M61" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
         <is>
           <t>留着翻身</t>
         </is>
       </c>
-      <c r="I61" s="3" t="inlineStr"/>
-      <c r="J61" s="3" t="inlineStr"/>
-      <c r="K61" s="3" t="inlineStr"/>
-      <c r="L61" s="3" t="inlineStr"/>
-      <c r="M61" s="3" t="inlineStr"/>
-      <c r="N61" s="3" t="inlineStr"/>
-      <c r="O61" s="4" t="n">
+      <c r="O61" s="2" t="inlineStr"/>
+      <c r="P61" s="2" t="inlineStr"/>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="P61" s="5" t="n">
+      <c r="V61" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="Q61" s="3" t="inlineStr"/>
-      <c r="R61" s="3" t="inlineStr"/>
-      <c r="S61" s="3" t="inlineStr"/>
-      <c r="T61" s="3" t="inlineStr">
+      <c r="W61" s="2" t="inlineStr"/>
+      <c r="X61" s="2" t="inlineStr"/>
+      <c r="Y61" s="2" t="inlineStr"/>
+      <c r="Z61" s="2" t="inlineStr">
         <is>
           <t>还 6,000</t>
         </is>
       </c>
-      <c r="U61" s="3" t="inlineStr"/>
-      <c r="V61" s="3" t="inlineStr"/>
-      <c r="W61" s="3" t="inlineStr"/>
-      <c r="X61" s="3" t="inlineStr"/>
-      <c r="Y61" s="5" t="n">
+      <c r="AA61" s="2" t="inlineStr"/>
+      <c r="AB61" s="2" t="inlineStr"/>
+      <c r="AC61" s="2" t="inlineStr"/>
+      <c r="AD61" s="2" t="inlineStr"/>
+      <c r="AE61" s="5" t="n">
         <v>6000</v>
       </c>
-      <c r="Z61" s="3" t="inlineStr"/>
-      <c r="AA61" s="5" t="n">
+      <c r="AF61" s="2" t="inlineStr"/>
+      <c r="AG61" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="AB61" s="4" t="n">
+      <c r="AH61" s="4" t="n">
         <v>-7</v>
       </c>
-      <c r="AC61" s="3" t="inlineStr"/>
-      <c r="AD61" s="3" t="inlineStr"/>
-      <c r="AE61" s="3" t="inlineStr"/>
+      <c r="AI61" s="2" t="inlineStr"/>
+      <c r="AJ61" s="2" t="inlineStr"/>
+      <c r="AK61" s="2" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>c061</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="3" t="inlineStr">
         <is>
+          <t>risk_dca_01</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
           <t>网友</t>
         </is>
       </c>
-      <c r="C62" s="3" t="inlineStr">
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>wangyou</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>💬</t>
         </is>
       </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>风险</t>
         </is>
       </c>
-      <c r="E62" s="3" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr">
         <is>
           <t>别天天看了，每月固定买一点就行，长期拿着。</t>
         </is>
       </c>
-      <c r="F62" s="3" t="inlineStr"/>
-      <c r="G62" s="3" t="inlineStr"/>
-      <c r="H62" s="3" t="inlineStr">
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="2" t="inlineStr"/>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M62" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
         <is>
           <t>我就是要择时</t>
         </is>
       </c>
-      <c r="I62" s="3" t="inlineStr"/>
-      <c r="J62" s="3" t="inlineStr"/>
-      <c r="K62" s="3" t="inlineStr"/>
-      <c r="L62" s="3" t="inlineStr"/>
-      <c r="M62" s="3" t="inlineStr"/>
-      <c r="N62" s="3" t="inlineStr"/>
-      <c r="O62" s="4" t="n">
+      <c r="O62" s="2" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr"/>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="P62" s="3" t="inlineStr"/>
-      <c r="Q62" s="3" t="inlineStr"/>
-      <c r="R62" s="3" t="inlineStr"/>
-      <c r="S62" s="3" t="inlineStr"/>
-      <c r="T62" s="3" t="inlineStr">
+      <c r="V62" s="2" t="inlineStr"/>
+      <c r="W62" s="2" t="inlineStr"/>
+      <c r="X62" s="2" t="inlineStr"/>
+      <c r="Y62" s="2" t="inlineStr"/>
+      <c r="Z62" s="2" t="inlineStr">
         <is>
           <t>每月投 2,000</t>
         </is>
       </c>
-      <c r="U62" s="3" t="inlineStr"/>
-      <c r="V62" s="5" t="n">
+      <c r="AA62" s="2" t="inlineStr"/>
+      <c r="AB62" s="5" t="n">
         <v>2000</v>
       </c>
-      <c r="W62" s="3" t="inlineStr"/>
-      <c r="X62" s="3" t="inlineStr"/>
-      <c r="Y62" s="3" t="inlineStr"/>
-      <c r="Z62" s="3" t="inlineStr"/>
-      <c r="AA62" s="5" t="n">
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr"/>
+      <c r="AE62" s="2" t="inlineStr"/>
+      <c r="AF62" s="2" t="inlineStr"/>
+      <c r="AG62" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="AB62" s="3" t="inlineStr"/>
-      <c r="AC62" s="3" t="inlineStr"/>
-      <c r="AD62" s="3" t="inlineStr"/>
-      <c r="AE62" s="3" t="inlineStr"/>
+      <c r="AH62" s="2" t="inlineStr"/>
+      <c r="AI62" s="2" t="inlineStr"/>
+      <c r="AJ62" s="2" t="inlineStr"/>
+      <c r="AK62" s="2" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>c062</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="3" t="inlineStr">
         <is>
+          <t>risk_scoreboard_01</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
           <t>年度账单</t>
         </is>
       </c>
-      <c r="C63" s="3" t="inlineStr">
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>nianduzhangdan</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>📊</t>
         </is>
       </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>风险</t>
         </is>
       </c>
-      <c r="E63" s="3" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>你今年的收益，跑赢了 1.2% 的人。</t>
         </is>
       </c>
-      <c r="F63" s="3" t="inlineStr"/>
-      <c r="G63" s="3" t="inlineStr"/>
-      <c r="H63" s="3" t="inlineStr">
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="2" t="inlineStr"/>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M63" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
         <is>
           <t>删掉 App</t>
         </is>
       </c>
-      <c r="I63" s="3" t="inlineStr"/>
-      <c r="J63" s="3" t="inlineStr"/>
-      <c r="K63" s="3" t="inlineStr"/>
-      <c r="L63" s="3" t="inlineStr"/>
-      <c r="M63" s="3" t="inlineStr"/>
-      <c r="N63" s="3" t="inlineStr"/>
-      <c r="O63" s="4" t="n">
+      <c r="O63" s="2" t="inlineStr"/>
+      <c r="P63" s="2" t="inlineStr"/>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="4" t="n">
         <v>-2</v>
       </c>
-      <c r="P63" s="4" t="n">
+      <c r="V63" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="Q63" s="3" t="inlineStr"/>
-      <c r="R63" s="3" t="inlineStr"/>
-      <c r="S63" s="3" t="inlineStr"/>
-      <c r="T63" s="3" t="inlineStr">
+      <c r="W63" s="2" t="inlineStr"/>
+      <c r="X63" s="2" t="inlineStr"/>
+      <c r="Y63" s="2" t="inlineStr"/>
+      <c r="Z63" s="2" t="inlineStr">
         <is>
           <t>再来一年</t>
         </is>
       </c>
-      <c r="U63" s="3" t="inlineStr"/>
-      <c r="V63" s="3" t="inlineStr"/>
-      <c r="W63" s="3" t="inlineStr"/>
-      <c r="X63" s="3" t="inlineStr"/>
-      <c r="Y63" s="3" t="inlineStr"/>
-      <c r="Z63" s="3" t="inlineStr"/>
-      <c r="AA63" s="4" t="n">
+      <c r="AA63" s="2" t="inlineStr"/>
+      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr"/>
+      <c r="AD63" s="2" t="inlineStr"/>
+      <c r="AE63" s="2" t="inlineStr"/>
+      <c r="AF63" s="2" t="inlineStr"/>
+      <c r="AG63" s="4" t="n">
         <v>-5</v>
       </c>
-      <c r="AB63" s="3" t="inlineStr"/>
-      <c r="AC63" s="3" t="inlineStr"/>
-      <c r="AD63" s="3" t="inlineStr"/>
-      <c r="AE63" s="3" t="inlineStr"/>
+      <c r="AH63" s="2" t="inlineStr"/>
+      <c r="AI63" s="2" t="inlineStr"/>
+      <c r="AJ63" s="2" t="inlineStr"/>
+      <c r="AK63" s="2" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>c063</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="3" t="inlineStr">
         <is>
+          <t>acc_cat_01</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
           <t>你的猫</t>
         </is>
       </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>nidemao</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>🐱</t>
         </is>
       </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>意外</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr">
         <is>
           <t>猫从键盘上踩过去。等你回过神，一笔 8,000 已经买进去了。</t>
         </is>
       </c>
-      <c r="F64" s="3" t="inlineStr"/>
-      <c r="G64" s="3" t="inlineStr"/>
-      <c r="H64" s="3" t="inlineStr">
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="2" t="inlineStr"/>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M64" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
         <is>
           <t>赶紧撤单</t>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr"/>
-      <c r="J64" s="3" t="inlineStr"/>
-      <c r="K64" s="3" t="inlineStr"/>
-      <c r="L64" s="3" t="inlineStr"/>
-      <c r="M64" s="3" t="inlineStr"/>
-      <c r="N64" s="3" t="inlineStr"/>
-      <c r="O64" s="4" t="n">
+      <c r="O64" s="2" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr"/>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="4" t="n">
         <v>-3</v>
       </c>
-      <c r="P64" s="3" t="inlineStr"/>
-      <c r="Q64" s="3" t="inlineStr"/>
-      <c r="R64" s="3" t="inlineStr"/>
-      <c r="S64" s="3" t="inlineStr"/>
-      <c r="T64" s="3" t="inlineStr">
+      <c r="V64" s="2" t="inlineStr"/>
+      <c r="W64" s="2" t="inlineStr"/>
+      <c r="X64" s="2" t="inlineStr"/>
+      <c r="Y64" s="2" t="inlineStr"/>
+      <c r="Z64" s="2" t="inlineStr">
         <is>
           <t>就当长线投资</t>
         </is>
       </c>
-      <c r="U64" s="3" t="inlineStr"/>
-      <c r="V64" s="5" t="n">
+      <c r="AA64" s="2" t="inlineStr"/>
+      <c r="AB64" s="5" t="n">
         <v>8000</v>
       </c>
-      <c r="W64" s="3" t="inlineStr"/>
-      <c r="X64" s="3" t="inlineStr"/>
-      <c r="Y64" s="3" t="inlineStr"/>
-      <c r="Z64" s="3" t="inlineStr"/>
-      <c r="AA64" s="4" t="n">
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr"/>
+      <c r="AE64" s="2" t="inlineStr"/>
+      <c r="AF64" s="2" t="inlineStr"/>
+      <c r="AG64" s="4" t="n">
         <v>-4</v>
       </c>
-      <c r="AB64" s="3" t="inlineStr"/>
-      <c r="AC64" s="3" t="inlineStr"/>
-      <c r="AD64" s="3" t="inlineStr"/>
-      <c r="AE64" s="3" t="inlineStr"/>
+      <c r="AH64" s="2" t="inlineStr"/>
+      <c r="AI64" s="2" t="inlineStr"/>
+      <c r="AJ64" s="2" t="inlineStr"/>
+      <c r="AK64" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AE64"/>
+  <autoFilter ref="A1:AK64"/>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"人情,决策,家庭,市场,意外,收入,职场,自己,风险"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/cards.xlsx
+++ b/data/cards.xlsx
@@ -11,7 +11,7 @@
     <sheet name="填表说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'卡牌数值'!$A$1:$AK$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'卡牌数值'!$A$1:$AK$98</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK64"/>
+  <dimension ref="A1:AK98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6.388888888888888" customWidth="1" min="1" max="1"/>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>女儿</t>
+          <t>孩子</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>nver</t>
+          <t>haizi</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -4040,12 +4040,12 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>新闻联播</t>
+          <t>新闻</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>xinwenlianbo</t>
+          <t>xinwen</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>新闻头条</t>
+          <t>新闻</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>xinwentoutiao</t>
+          <t>xinwen</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>公司群</t>
+          <t>新闻</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>gongsiqun</t>
+          <t>xinwen</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -6063,10 +6063,2874 @@
       <c r="AJ64" s="2" t="inlineStr"/>
       <c r="AK64" s="2" t="inlineStr"/>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>fam_reportcard_01</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>孩子</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>haizi</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>🧒</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>家庭</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>孩子举着卷子过来。你摆摆手：「等一下。」</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="2" t="inlineStr"/>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M65" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>等一下</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr"/>
+      <c r="P65" s="2" t="inlineStr"/>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V65" s="2" t="inlineStr"/>
+      <c r="W65" s="4" t="n">
+        <v>-8</v>
+      </c>
+      <c r="X65" s="2" t="inlineStr"/>
+      <c r="Y65" s="2" t="inlineStr"/>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>现在就签</t>
+        </is>
+      </c>
+      <c r="AA65" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr"/>
+      <c r="AE65" s="2" t="inlineStr"/>
+      <c r="AF65" s="2" t="inlineStr"/>
+      <c r="AG65" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH65" s="2" t="inlineStr"/>
+      <c r="AI65" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ65" s="2" t="inlineStr"/>
+      <c r="AK65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>fam_laopo_02</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>老婆</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>laopo</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>💍</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>家庭</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>「今晚吃什么？」你盯着 K 线，回了句「随便」。</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="2" t="inlineStr"/>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M66" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>随便</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr"/>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V66" s="2" t="inlineStr"/>
+      <c r="W66" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="X66" s="2" t="inlineStr"/>
+      <c r="Y66" s="2" t="inlineStr"/>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>放下手机问她</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr"/>
+      <c r="AB66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr"/>
+      <c r="AE66" s="2" t="inlineStr"/>
+      <c r="AF66" s="2" t="inlineStr"/>
+      <c r="AG66" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH66" s="2" t="inlineStr"/>
+      <c r="AI66" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ66" s="2" t="inlineStr"/>
+      <c r="AK66" s="2" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>fam_inlaws_02</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>丈母娘</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>zhangmuniang</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>👵</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>家庭</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>饭桌上，丈母娘随口问：「今年，攒下了吧？」</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M67" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>还行，还行</t>
+        </is>
+      </c>
+      <c r="O67" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="P67" s="2" t="inlineStr"/>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr"/>
+      <c r="W67" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="X67" s="2" t="inlineStr"/>
+      <c r="Y67" s="2" t="inlineStr"/>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>说了实话</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr"/>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr"/>
+      <c r="AE67" s="2" t="inlineStr"/>
+      <c r="AF67" s="2" t="inlineStr"/>
+      <c r="AG67" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH67" s="2" t="inlineStr"/>
+      <c r="AI67" s="4" t="n">
+        <v>-7</v>
+      </c>
+      <c r="AJ67" s="2" t="inlineStr"/>
+      <c r="AK67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>work_follower_01</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>同事小王</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>tongshi_xiaowang</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>👔</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>职场</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>小王压低声音：「哥，你买啥，我跟着买。」</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M68" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>别跟着我</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr"/>
+      <c r="P68" s="2" t="inlineStr"/>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V68" s="2" t="inlineStr"/>
+      <c r="W68" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="X68" s="2" t="inlineStr"/>
+      <c r="Y68" s="2" t="inlineStr"/>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>把持仓给他看</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr"/>
+      <c r="AB68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr"/>
+      <c r="AE68" s="2" t="inlineStr"/>
+      <c r="AF68" s="2" t="inlineStr"/>
+      <c r="AG68" s="2" t="inlineStr"/>
+      <c r="AH68" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI68" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ68" s="2" t="inlineStr"/>
+      <c r="AK68" s="2" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>work_review_01</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>hr</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>🗂</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>职场</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>HR 笑着说：「聊聊你下半年的规划吧。」</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr"/>
+      <c r="I69" s="2" t="inlineStr"/>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M69" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>表了个态</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr"/>
+      <c r="P69" s="2" t="inlineStr"/>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="4" t="n">
+        <v>-8</v>
+      </c>
+      <c r="V69" s="2" t="inlineStr"/>
+      <c r="W69" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X69" s="2" t="inlineStr"/>
+      <c r="Y69" s="2" t="inlineStr"/>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>问补偿方案</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr"/>
+      <c r="AB69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr"/>
+      <c r="AE69" s="2" t="inlineStr"/>
+      <c r="AF69" s="2" t="inlineStr"/>
+      <c r="AG69" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH69" s="2" t="inlineStr"/>
+      <c r="AI69" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ69" s="2" t="inlineStr"/>
+      <c r="AK69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>self_night_02</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>凌晨三点</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>lingsan</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>🌙</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>自己</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>凌晨三点。美股开盘了，你算了算明天的账。</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr"/>
+      <c r="I70" s="2" t="inlineStr"/>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M70" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>接着算</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr"/>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="V70" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="W70" s="2" t="inlineStr"/>
+      <c r="X70" s="2" t="inlineStr"/>
+      <c r="Y70" s="2" t="inlineStr"/>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>扣下手机</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr"/>
+      <c r="AB70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr"/>
+      <c r="AE70" s="2" t="inlineStr"/>
+      <c r="AF70" s="2" t="inlineStr"/>
+      <c r="AG70" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AH70" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI70" s="2" t="inlineStr"/>
+      <c r="AJ70" s="2" t="inlineStr"/>
+      <c r="AK70" s="2" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>risk_bill_01</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>你的债</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>nidezhai</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>🧾</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>风险</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>账单日到了。你数了数，还差四千。</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M71" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>再借一笔</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr"/>
+      <c r="P71" s="2" t="inlineStr"/>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="5" t="n">
+        <v>4000</v>
+      </c>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V71" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="W71" s="2" t="inlineStr"/>
+      <c r="X71" s="2" t="inlineStr"/>
+      <c r="Y71" s="2" t="inlineStr"/>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>卖点票周转</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr"/>
+      <c r="AB71" s="2" t="inlineStr"/>
+      <c r="AC71" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AD71" s="2" t="inlineStr"/>
+      <c r="AE71" s="2" t="inlineStr"/>
+      <c r="AF71" s="2" t="inlineStr"/>
+      <c r="AG71" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH71" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AI71" s="2" t="inlineStr"/>
+      <c r="AJ71" s="2" t="inlineStr"/>
+      <c r="AK71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>mkt_headline_01</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>新闻</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>xinwen</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>📰</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>市场</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>头条推送：「重磅利好，明天开盘见分晓。」</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="2" t="inlineStr"/>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M72" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>激动转发</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr"/>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V72" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="W72" s="2" t="inlineStr"/>
+      <c r="X72" s="2" t="inlineStr"/>
+      <c r="Y72" s="2" t="inlineStr"/>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>关掉推送</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr"/>
+      <c r="AB72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr"/>
+      <c r="AE72" s="2" t="inlineStr"/>
+      <c r="AF72" s="2" t="inlineStr"/>
+      <c r="AG72" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH72" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AI72" s="2" t="inlineStr"/>
+      <c r="AJ72" s="2" t="inlineStr"/>
+      <c r="AK72" s="2" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>soc_insider_01</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>张阿姨</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>zhangayi</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>🧶</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>人情</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>张阿姨拉住你：「有个内部渠道，稳得很。」</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M73" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>婉拒了</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr"/>
+      <c r="P73" s="2" t="inlineStr"/>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V73" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W73" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="X73" s="2" t="inlineStr"/>
+      <c r="Y73" s="2" t="inlineStr"/>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>投五千试试</t>
+        </is>
+      </c>
+      <c r="AA73" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="AB73" s="2" t="inlineStr"/>
+      <c r="AC73" s="2" t="inlineStr"/>
+      <c r="AD73" s="2" t="inlineStr"/>
+      <c r="AE73" s="2" t="inlineStr"/>
+      <c r="AF73" s="2" t="inlineStr"/>
+      <c r="AG73" s="2" t="inlineStr"/>
+      <c r="AH73" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI73" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ73" s="2" t="inlineStr"/>
+      <c r="AK73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>self_mirror_02</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>镜子</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>jingzi</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>🪞</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>自己</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>镜子里的人眼下乌青，像在问：还来吗？</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>mind&lt;45</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M74" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>再战一次</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr"/>
+      <c r="P74" s="2" t="inlineStr"/>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V74" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="W74" s="2" t="inlineStr"/>
+      <c r="X74" s="2" t="inlineStr"/>
+      <c r="Y74" s="2" t="inlineStr"/>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>笑了笑，没说话</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr"/>
+      <c r="AB74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr"/>
+      <c r="AE74" s="2" t="inlineStr"/>
+      <c r="AF74" s="2" t="inlineStr"/>
+      <c r="AG74" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH74" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AI74" s="2" t="inlineStr"/>
+      <c r="AJ74" s="2" t="inlineStr"/>
+      <c r="AK74" s="2" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>fam_momcall_01</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>老妈</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>laoma</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>📞</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>家庭</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>老妈来电话，问吃了没。你嗯嗯两声，眼睛没离开盘面。</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr"/>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M75" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>嗯嗯两声</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr"/>
+      <c r="P75" s="2" t="inlineStr"/>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" s="2" t="inlineStr"/>
+      <c r="W75" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="X75" s="2" t="inlineStr"/>
+      <c r="Y75" s="2" t="inlineStr"/>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>回厨房看她</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr"/>
+      <c r="AB75" s="2" t="inlineStr"/>
+      <c r="AC75" s="2" t="inlineStr"/>
+      <c r="AD75" s="2" t="inlineStr"/>
+      <c r="AE75" s="2" t="inlineStr"/>
+      <c r="AF75" s="2" t="inlineStr"/>
+      <c r="AG75" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH75" s="2" t="inlineStr"/>
+      <c r="AI75" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ75" s="2" t="inlineStr"/>
+      <c r="AK75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>fam_momhealth_01</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>老妈</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>laoma</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>📞</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>家庭</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>老妈拍来一张体检单：她血压也高了。</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr"/>
+      <c r="I76" s="2" t="inlineStr"/>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M76" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>让她别操心</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr"/>
+      <c r="P76" s="2" t="inlineStr"/>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="V76" s="2" t="inlineStr"/>
+      <c r="W76" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="X76" s="2" t="inlineStr"/>
+      <c r="Y76" s="2" t="inlineStr"/>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>预约陪复查</t>
+        </is>
+      </c>
+      <c r="AA76" s="5" t="n">
+        <v>800</v>
+      </c>
+      <c r="AB76" s="2" t="inlineStr"/>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr"/>
+      <c r="AE76" s="2" t="inlineStr"/>
+      <c r="AF76" s="2" t="inlineStr"/>
+      <c r="AG76" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH76" s="2" t="inlineStr"/>
+      <c r="AI76" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ76" s="2" t="inlineStr"/>
+      <c r="AK76" s="2" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="3" t="inlineStr">
+        <is>
+          <t>fam_landlordfix_01</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>房东</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>fangdong</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>🔧</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>家庭</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>热水器坏了三天。房东说：找人，要等下周。</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr"/>
+      <c r="I77" s="2" t="inlineStr"/>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M77" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>自己找人修</t>
+        </is>
+      </c>
+      <c r="O77" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="P77" s="2" t="inlineStr"/>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V77" s="2" t="inlineStr"/>
+      <c r="W77" s="2" t="inlineStr"/>
+      <c r="X77" s="2" t="inlineStr"/>
+      <c r="Y77" s="2" t="inlineStr"/>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>等下周</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr"/>
+      <c r="AB77" s="2" t="inlineStr"/>
+      <c r="AC77" s="2" t="inlineStr"/>
+      <c r="AD77" s="2" t="inlineStr"/>
+      <c r="AE77" s="2" t="inlineStr"/>
+      <c r="AF77" s="2" t="inlineStr"/>
+      <c r="AG77" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH77" s="2" t="inlineStr"/>
+      <c r="AI77" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AJ77" s="2" t="inlineStr"/>
+      <c r="AK77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>fam_teacher_01</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>老师</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>laoshi</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>🎓</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>家庭</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>班主任来电话：孩子最近上课，总是走神。</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr"/>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M78" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>说最近忙</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr"/>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V78" s="2" t="inlineStr"/>
+      <c r="W78" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="X78" s="2" t="inlineStr"/>
+      <c r="Y78" s="2" t="inlineStr"/>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>当晚陪作业</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr"/>
+      <c r="AB78" s="2" t="inlineStr"/>
+      <c r="AC78" s="2" t="inlineStr"/>
+      <c r="AD78" s="2" t="inlineStr"/>
+      <c r="AE78" s="2" t="inlineStr"/>
+      <c r="AF78" s="2" t="inlineStr"/>
+      <c r="AG78" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AH78" s="2" t="inlineStr"/>
+      <c r="AI78" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ78" s="2" t="inlineStr"/>
+      <c r="AK78" s="2" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>fam_anniv_01</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>老婆</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>laopo</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>💍</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>家庭</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>日历提醒：结婚纪念日。同一天，晚上八点半，非农。</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="2" t="inlineStr"/>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M79" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>订了餐厅</t>
+        </is>
+      </c>
+      <c r="O79" s="5" t="n">
+        <v>900</v>
+      </c>
+      <c r="P79" s="2" t="inlineStr"/>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="V79" s="2" t="inlineStr"/>
+      <c r="W79" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="X79" s="2" t="inlineStr"/>
+      <c r="Y79" s="2" t="inlineStr"/>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>说明年补</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr"/>
+      <c r="AB79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr"/>
+      <c r="AE79" s="2" t="inlineStr"/>
+      <c r="AF79" s="2" t="inlineStr"/>
+      <c r="AG79" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH79" s="2" t="inlineStr"/>
+      <c r="AI79" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="AJ79" s="2" t="inlineStr"/>
+      <c r="AK79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>fam_kidsfee_01</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>孩子</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>haizi</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>🧒</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>家庭</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>兴趣班要续费 6,800。他说，其实不想去了。</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="2" t="inlineStr"/>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M80" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>续费</t>
+        </is>
+      </c>
+      <c r="O80" s="5" t="n">
+        <v>6800</v>
+      </c>
+      <c r="P80" s="2" t="inlineStr"/>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V80" s="2" t="inlineStr"/>
+      <c r="W80" s="2" t="inlineStr"/>
+      <c r="X80" s="2" t="inlineStr"/>
+      <c r="Y80" s="2" t="inlineStr"/>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>退班，陪他玩</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr"/>
+      <c r="AB80" s="2" t="inlineStr"/>
+      <c r="AC80" s="2" t="inlineStr"/>
+      <c r="AD80" s="2" t="inlineStr"/>
+      <c r="AE80" s="2" t="inlineStr"/>
+      <c r="AF80" s="2" t="inlineStr"/>
+      <c r="AG80" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH80" s="2" t="inlineStr"/>
+      <c r="AI80" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ80" s="2" t="inlineStr"/>
+      <c r="AK80" s="2" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="3" t="inlineStr">
+        <is>
+          <t>fam_prenatal_01</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>老婆</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>laopo</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>💍</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>家庭</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>产检约在周四上午。她说：你来吧。</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>has:baby</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr"/>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M81" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>陪她去</t>
+        </is>
+      </c>
+      <c r="O81" s="5" t="n">
+        <v>1200</v>
+      </c>
+      <c r="P81" s="2" t="inlineStr"/>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V81" s="2" t="inlineStr"/>
+      <c r="W81" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="X81" s="2" t="inlineStr"/>
+      <c r="Y81" s="2" t="inlineStr"/>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>让她妈陪</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr"/>
+      <c r="AB81" s="2" t="inlineStr"/>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr"/>
+      <c r="AE81" s="2" t="inlineStr"/>
+      <c r="AF81" s="2" t="inlineStr"/>
+      <c r="AG81" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH81" s="2" t="inlineStr"/>
+      <c r="AI81" s="4" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AJ81" s="2" t="inlineStr"/>
+      <c r="AK81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>fam_inlaws_03</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>丈母娘</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>zhangmuniang</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>👵</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>家庭</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>丈母娘生日。红包行情，你研究了一晚上。</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M82" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>包 6,600</t>
+        </is>
+      </c>
+      <c r="O82" s="5" t="n">
+        <v>6600</v>
+      </c>
+      <c r="P82" s="2" t="inlineStr"/>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr"/>
+      <c r="W82" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="X82" s="2" t="inlineStr"/>
+      <c r="Y82" s="2" t="inlineStr"/>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>包 1,600</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr"/>
+      <c r="AB82" s="2" t="inlineStr"/>
+      <c r="AC82" s="2" t="inlineStr"/>
+      <c r="AD82" s="2" t="inlineStr"/>
+      <c r="AE82" s="2" t="inlineStr"/>
+      <c r="AF82" s="2" t="inlineStr"/>
+      <c r="AG82" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH82" s="2" t="inlineStr"/>
+      <c r="AI82" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AJ82" s="2" t="inlineStr"/>
+      <c r="AK82" s="2" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>work_bossmeet_01</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>老板</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>laoban</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>📋</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>职场</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>例会上你走神了。老板停顿两秒，点了你的名。</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="2" t="inlineStr"/>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M83" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>承认走神</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr"/>
+      <c r="P83" s="2" t="inlineStr"/>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V83" s="2" t="inlineStr"/>
+      <c r="W83" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="X83" s="2" t="inlineStr"/>
+      <c r="Y83" s="2" t="inlineStr"/>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>找理由圆</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr"/>
+      <c r="AB83" s="2" t="inlineStr"/>
+      <c r="AC83" s="2" t="inlineStr"/>
+      <c r="AD83" s="2" t="inlineStr"/>
+      <c r="AE83" s="2" t="inlineStr"/>
+      <c r="AF83" s="2" t="inlineStr"/>
+      <c r="AG83" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AH83" s="2" t="inlineStr"/>
+      <c r="AI83" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ83" s="2" t="inlineStr"/>
+      <c r="AK83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>work_raise_01</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>老板</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>laoban</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>📋</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>职场</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>调薪名单出了。你从头看到尾，没有你。</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="2" t="inlineStr"/>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M84" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>忍了</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr"/>
+      <c r="P84" s="2" t="inlineStr"/>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="V84" s="2" t="inlineStr"/>
+      <c r="W84" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X84" s="2" t="inlineStr"/>
+      <c r="Y84" s="2" t="inlineStr"/>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>去找他谈</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr"/>
+      <c r="AB84" s="2" t="inlineStr"/>
+      <c r="AC84" s="2" t="inlineStr"/>
+      <c r="AD84" s="2" t="inlineStr"/>
+      <c r="AE84" s="2" t="inlineStr"/>
+      <c r="AF84" s="2" t="inlineStr"/>
+      <c r="AG84" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH84" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI84" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ84" s="2" t="inlineStr"/>
+      <c r="AK84" s="2" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>work_headhunt_01</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>招聘软件</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>zhaopin</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>📱</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>职场</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>猎头：薪资涨三成。背景调查会联系现公司。</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M85" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>回绝了</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr"/>
+      <c r="P85" s="2" t="inlineStr"/>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V85" s="2" t="inlineStr"/>
+      <c r="W85" s="2" t="inlineStr"/>
+      <c r="X85" s="2" t="inlineStr"/>
+      <c r="Y85" s="2" t="inlineStr"/>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>聊聊看</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr"/>
+      <c r="AB85" s="2" t="inlineStr"/>
+      <c r="AC85" s="2" t="inlineStr"/>
+      <c r="AD85" s="2" t="inlineStr"/>
+      <c r="AE85" s="2" t="inlineStr"/>
+      <c r="AF85" s="2" t="inlineStr"/>
+      <c r="AG85" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH85" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI85" s="2" t="inlineStr"/>
+      <c r="AJ85" s="2" t="inlineStr"/>
+      <c r="AK85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>work_ref_01</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>老同事</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>laotongshi</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>🤝</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>职场</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>老同事内推：他那边在招人，问你要不要投。</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="2" t="inlineStr"/>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M86" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>投了简历</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr"/>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V86" s="2" t="inlineStr"/>
+      <c r="W86" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X86" s="2" t="inlineStr"/>
+      <c r="Y86" s="2" t="inlineStr"/>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>没投</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr"/>
+      <c r="AB86" s="2" t="inlineStr"/>
+      <c r="AC86" s="2" t="inlineStr"/>
+      <c r="AD86" s="2" t="inlineStr"/>
+      <c r="AE86" s="2" t="inlineStr"/>
+      <c r="AF86" s="2" t="inlineStr"/>
+      <c r="AG86" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH86" s="2" t="inlineStr"/>
+      <c r="AI86" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AJ86" s="2" t="inlineStr"/>
+      <c r="AK86" s="2" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="3" t="inlineStr">
+        <is>
+          <t>work_xiaowang_02</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>同事小王</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>tongshi_xiaowang</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>👔</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>职场</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>小王开口：借 5,000 补仓，下个月一定还。</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr"/>
+      <c r="I87" s="2" t="inlineStr"/>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M87" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>借了</t>
+        </is>
+      </c>
+      <c r="O87" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="P87" s="2" t="inlineStr"/>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="W87" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="X87" s="2" t="inlineStr"/>
+      <c r="Y87" s="2" t="inlineStr"/>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>拒绝了</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr"/>
+      <c r="AB87" s="2" t="inlineStr"/>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr"/>
+      <c r="AE87" s="2" t="inlineStr"/>
+      <c r="AF87" s="2" t="inlineStr"/>
+      <c r="AG87" s="4" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AH87" s="2" t="inlineStr"/>
+      <c r="AI87" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="AJ87" s="2" t="inlineStr"/>
+      <c r="AK87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>work_screen_01</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>项目</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>xiangmu</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>📊</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>职场</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>项目明早上线。今晚，你在改自己的止损位。</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr"/>
+      <c r="I88" s="2" t="inlineStr"/>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M88" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>改完再说</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr"/>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V88" s="2" t="inlineStr"/>
+      <c r="W88" s="4" t="n">
+        <v>-7</v>
+      </c>
+      <c r="X88" s="2" t="inlineStr"/>
+      <c r="Y88" s="2" t="inlineStr"/>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>专心上线</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr"/>
+      <c r="AB88" s="2" t="inlineStr"/>
+      <c r="AC88" s="2" t="inlineStr"/>
+      <c r="AD88" s="2" t="inlineStr"/>
+      <c r="AE88" s="2" t="inlineStr"/>
+      <c r="AF88" s="2" t="inlineStr"/>
+      <c r="AG88" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="AH88" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI88" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AJ88" s="2" t="inlineStr"/>
+      <c r="AK88" s="2" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="3" t="inlineStr">
+        <is>
+          <t>self_checkup_02</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>体检报告</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>tijian</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>🩺</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>自己</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>复查单出来了。血压，还是高。</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr"/>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M89" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>吃药，早睡</t>
+        </is>
+      </c>
+      <c r="O89" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="P89" s="2" t="inlineStr"/>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V89" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="W89" s="2" t="inlineStr"/>
+      <c r="X89" s="2" t="inlineStr"/>
+      <c r="Y89" s="2" t="inlineStr"/>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>先放放</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr"/>
+      <c r="AB89" s="2" t="inlineStr"/>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr"/>
+      <c r="AE89" s="2" t="inlineStr"/>
+      <c r="AF89" s="2" t="inlineStr"/>
+      <c r="AG89" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH89" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI89" s="2" t="inlineStr"/>
+      <c r="AJ89" s="2" t="inlineStr"/>
+      <c r="AK89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>self_night_03</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>凌晨三点</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>lingsan</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>🌙</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>自己</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>睡前刷到群消息：明天，见分晓。</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M90" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>设了 3:50 闹钟</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr"/>
+      <c r="P90" s="2" t="inlineStr"/>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="V90" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="W90" s="2" t="inlineStr"/>
+      <c r="X90" s="2" t="inlineStr"/>
+      <c r="Y90" s="2" t="inlineStr"/>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>手机扔客厅</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr"/>
+      <c r="AB90" s="2" t="inlineStr"/>
+      <c r="AC90" s="2" t="inlineStr"/>
+      <c r="AD90" s="2" t="inlineStr"/>
+      <c r="AE90" s="2" t="inlineStr"/>
+      <c r="AF90" s="2" t="inlineStr"/>
+      <c r="AG90" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH90" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AI90" s="2" t="inlineStr"/>
+      <c r="AJ90" s="2" t="inlineStr"/>
+      <c r="AK90" s="2" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>self_weekend_02</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>周末</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>zhoumo</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>🛋</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>自己</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>周末两天。老婆说，回趟娘家吧。</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr"/>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M91" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>陪她回</t>
+        </is>
+      </c>
+      <c r="O91" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="P91" s="2" t="inlineStr"/>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V91" s="2" t="inlineStr"/>
+      <c r="W91" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="X91" s="2" t="inlineStr"/>
+      <c r="Y91" s="2" t="inlineStr"/>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>说要看盘</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr"/>
+      <c r="AB91" s="2" t="inlineStr"/>
+      <c r="AC91" s="2" t="inlineStr"/>
+      <c r="AD91" s="2" t="inlineStr"/>
+      <c r="AE91" s="2" t="inlineStr"/>
+      <c r="AF91" s="2" t="inlineStr"/>
+      <c r="AG91" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH91" s="2" t="inlineStr"/>
+      <c r="AI91" s="4" t="n">
+        <v>-9</v>
+      </c>
+      <c r="AJ91" s="2" t="inlineStr"/>
+      <c r="AK91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>self_birthday_02</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>生日</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>shengri</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>🎂</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>自己</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>生日这天。你打开账户，绿了。</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M92" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>关掉账户页</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr"/>
+      <c r="P92" s="2" t="inlineStr"/>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V92" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="W92" s="2" t="inlineStr"/>
+      <c r="X92" s="2" t="inlineStr"/>
+      <c r="Y92" s="2" t="inlineStr"/>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>截图发群里</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr"/>
+      <c r="AB92" s="2" t="inlineStr"/>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr"/>
+      <c r="AE92" s="2" t="inlineStr"/>
+      <c r="AF92" s="2" t="inlineStr"/>
+      <c r="AG92" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AH92" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI92" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AJ92" s="2" t="inlineStr"/>
+      <c r="AK92" s="2" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>self_dilou_02</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>地漏</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>dilou</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>🚿</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>自己</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>地漏又堵了。水漫过来，像某种预兆。</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
+      <c r="I93" s="2" t="inlineStr"/>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M93" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>叫师傅</t>
+        </is>
+      </c>
+      <c r="O93" s="5" t="n">
+        <v>200</v>
+      </c>
+      <c r="P93" s="2" t="inlineStr"/>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="V93" s="2" t="inlineStr"/>
+      <c r="W93" s="2" t="inlineStr"/>
+      <c r="X93" s="2" t="inlineStr"/>
+      <c r="Y93" s="2" t="inlineStr"/>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>明天再说</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr"/>
+      <c r="AB93" s="2" t="inlineStr"/>
+      <c r="AC93" s="2" t="inlineStr"/>
+      <c r="AD93" s="2" t="inlineStr"/>
+      <c r="AE93" s="2" t="inlineStr"/>
+      <c r="AF93" s="2" t="inlineStr"/>
+      <c r="AG93" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AH93" s="2" t="inlineStr"/>
+      <c r="AI93" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AJ93" s="2" t="inlineStr"/>
+      <c r="AK93" s="2" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>inc_salary_02</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>工资</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>gongzi</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>工资到账 9,600。你先算了算，这个月要还的。</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr"/>
+      <c r="I94" s="2" t="inlineStr"/>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M94" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>转一半补仓</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr"/>
+      <c r="P94" s="5" t="n">
+        <v>4800</v>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="V94" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="W94" s="2" t="inlineStr"/>
+      <c r="X94" s="2" t="inlineStr"/>
+      <c r="Y94" s="2" t="inlineStr"/>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>留着过活</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr"/>
+      <c r="AB94" s="2" t="inlineStr"/>
+      <c r="AC94" s="2" t="inlineStr"/>
+      <c r="AD94" s="2" t="inlineStr"/>
+      <c r="AE94" s="2" t="inlineStr"/>
+      <c r="AF94" s="2" t="inlineStr"/>
+      <c r="AG94" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH94" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="AI94" s="2" t="inlineStr"/>
+      <c r="AJ94" s="2" t="inlineStr"/>
+      <c r="AK94" s="2" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>inc_salary_03</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>工资</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>gongzi</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>💰</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>老板放话：下季度，可能调薪，也可能裁员。</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr"/>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M95" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>加把劲</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr"/>
+      <c r="P95" s="2" t="inlineStr"/>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="V95" s="2" t="inlineStr"/>
+      <c r="W95" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="X95" s="2" t="inlineStr"/>
+      <c r="Y95" s="2" t="inlineStr"/>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>偷偷更新简历</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr"/>
+      <c r="AB95" s="2" t="inlineStr"/>
+      <c r="AC95" s="2" t="inlineStr"/>
+      <c r="AD95" s="2" t="inlineStr"/>
+      <c r="AE95" s="2" t="inlineStr"/>
+      <c r="AF95" s="2" t="inlineStr"/>
+      <c r="AG95" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH95" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI95" s="2" t="inlineStr"/>
+      <c r="AJ95" s="2" t="inlineStr"/>
+      <c r="AK95" s="2" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>inc_sidejob_02</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>私活</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>sihuo</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>💻</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>收入</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>老客户来单：6,000。deadline 正好在财报周。</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr"/>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M96" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>接了</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr"/>
+      <c r="P96" s="2" t="inlineStr"/>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="5" t="n">
+        <v>6000</v>
+      </c>
+      <c r="U96" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="V96" s="2" t="inlineStr"/>
+      <c r="W96" s="4" t="n">
+        <v>-3</v>
+      </c>
+      <c r="X96" s="2" t="inlineStr"/>
+      <c r="Y96" s="2" t="inlineStr"/>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>推了</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr"/>
+      <c r="AB96" s="2" t="inlineStr"/>
+      <c r="AC96" s="2" t="inlineStr"/>
+      <c r="AD96" s="2" t="inlineStr"/>
+      <c r="AE96" s="2" t="inlineStr"/>
+      <c r="AF96" s="2" t="inlineStr"/>
+      <c r="AG96" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH96" s="2" t="inlineStr"/>
+      <c r="AI96" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ96" s="2" t="inlineStr"/>
+      <c r="AK96" s="2" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>soc_oldmate_01</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>老同学</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>laotongxue</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>🍺</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>人情</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>老同学组局。AA 每人 500。你怕聊起股票。</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr"/>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M97" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>去了</t>
+        </is>
+      </c>
+      <c r="O97" s="5" t="n">
+        <v>500</v>
+      </c>
+      <c r="P97" s="2" t="inlineStr"/>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="V97" s="2" t="inlineStr"/>
+      <c r="W97" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="X97" s="2" t="inlineStr"/>
+      <c r="Y97" s="2" t="inlineStr"/>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>没去</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr"/>
+      <c r="AB97" s="2" t="inlineStr"/>
+      <c r="AC97" s="2" t="inlineStr"/>
+      <c r="AD97" s="2" t="inlineStr"/>
+      <c r="AE97" s="2" t="inlineStr"/>
+      <c r="AF97" s="2" t="inlineStr"/>
+      <c r="AG97" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH97" s="2" t="inlineStr"/>
+      <c r="AI97" s="4" t="n">
+        <v>-5</v>
+      </c>
+      <c r="AJ97" s="2" t="inlineStr"/>
+      <c r="AK97" s="2" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="3" t="inlineStr">
+        <is>
+          <t>soc_lend_02</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>朋友</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>pengyou</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>🤝</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>人情</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>朋友开口：借两万。他说，这次一定还。</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr"/>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="M98" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>借一半</t>
+        </is>
+      </c>
+      <c r="O98" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="P98" s="2" t="inlineStr"/>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="W98" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="X98" s="2" t="inlineStr"/>
+      <c r="Y98" s="2" t="inlineStr"/>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>婉拒了</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr"/>
+      <c r="AB98" s="2" t="inlineStr"/>
+      <c r="AC98" s="2" t="inlineStr"/>
+      <c r="AD98" s="2" t="inlineStr"/>
+      <c r="AE98" s="2" t="inlineStr"/>
+      <c r="AF98" s="2" t="inlineStr"/>
+      <c r="AG98" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AH98" s="2" t="inlineStr"/>
+      <c r="AI98" s="4" t="n">
+        <v>-8</v>
+      </c>
+      <c r="AJ98" s="2" t="inlineStr"/>
+      <c r="AK98" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AK64"/>
+  <autoFilter ref="A1:AK98"/>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F64" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F2:F98" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"人情,决策,家庭,市场,意外,收入,职场,自己,风险"</formula1>
     </dataValidation>
   </dataValidations>
